--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R0d79530c361a4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Rb34295eaf4f9439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Rc5b9f3b27ee64fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R255495fd16b349d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R96466c51703c4418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rf99af46b52ac487f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Rc8ee22467f1b4650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R51d4b1ac680e4615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rcc2c8f9249b445fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R778a73e6703c4e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R3989c2a0fddb4bc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R3fb3674a73fa41ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rcc5d5077301640ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Red8cc1ecb20d4320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R94393acfbe0841cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R8e93b041c858461e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Rb3ffbb620a9540c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R73f499c8f11240d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rad9bb8cab28540f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R8500a64b32484738"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R8ffeb3d22d924c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R6b4728aefb824f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rba43826fd3aa4e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R3ecb93f54df846ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="Rddc3439a35b34dfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R0dcbdb0726fe4670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R0ea1770d2ff14d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R1e074750e0274725"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -75,7 +75,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -100,6 +100,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -4984,6 +4985,317 @@
         <x:v>Qube delisted 17 Aug 2026.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>NEWSV1251_01</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>Davie awarded C$11.3bn contract to build six Canadian Coast Guard Program Icebreakers</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>Davie, part of Inocea, secured a fixed-price C$11.3bn contract for six Program Icebreakers.</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I22" s="14" t="str">
+        <x:v>Shipbuilding / Arctic / Defence</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>Contract award</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="str">
+        <x:v>Icebreaker programme</x:v>
+      </x:c>
+      <x:c r="L22" s="14" t="str"/>
+      <x:c r="M22" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N22" s="14" t="str">
+        <x:v>SRC_V1251_002</x:v>
+      </x:c>
+      <x:c r="O22" s="14" t="str">
+        <x:v>Links Inocea, Davie and Arctic trade-support capacity.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>NEWSV1251_02</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>2025-12-02</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>Davie Defense closes acquisition of Gulf Copper shipbuilding assets in Texas</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>Davie</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>https://www.davie.ca/en/news/davie-defense-closes-gulf-copper-acquisition-confirming-u-s-shipbuilding-expansion/</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>Davie Defense completed its acquisition of Gulf Copper shipbuilding assets in Galveston and Port Arthur.</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="I23" s="14" t="str">
+        <x:v>Shipbuilding / M&amp;A</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="str">
+        <x:v>Transaction</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="str">
+        <x:v>Acquisition completed</x:v>
+      </x:c>
+      <x:c r="L23" s="14" t="str"/>
+      <x:c r="M23" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N23" s="14" t="str">
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+      <x:c r="O23" s="14" t="str">
+        <x:v>Expands Inocea's U.S. industrial footprint.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>NEWSV1251_03</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>Seaspan and Maersk advance fleet-efficiency upgrade programme across 18 chartered vessels</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>Seaspan Corporation</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/news/seaspan-and-maersk-advance-fleet-efficiency-through-strategic-vessel-upgrade-program/</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>Seaspan and Maersk are advancing efficiency upgrades across 18 long-term chartered vessels.</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str"/>
+      <x:c r="I24" s="14" t="str">
+        <x:v>Shipping / Fleet / Decarbonisation</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="str">
+        <x:v>Fleet programme</x:v>
+      </x:c>
+      <x:c r="K24" s="14" t="str">
+        <x:v>Retrofit / charter partnership</x:v>
+      </x:c>
+      <x:c r="L24" s="14" t="str"/>
+      <x:c r="M24" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N24" s="14" t="str">
+        <x:v>SRC_V1251_007</x:v>
+      </x:c>
+      <x:c r="O24" s="14" t="str">
+        <x:v>Links shipowner, charterer and vessel fleet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>NEWSV1251_04</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>Seaspan receives investment-grade issuer rating upgrade from KBRA</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>Seaspan Corporation</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>https://www.seaspancorp.com/news/seaspan-achieves-investment-grade-rating-upgrade-from-kbra/</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str">
+        <x:v>KBRA upgraded Seaspan's issuer and senior unsecured ratings to BBB-.</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str"/>
+      <x:c r="I25" s="14" t="str">
+        <x:v>Shipping / Finance</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="str">
+        <x:v>Corporate / credit</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>Rating upgrade</x:v>
+      </x:c>
+      <x:c r="L25" s="14" t="str"/>
+      <x:c r="M25" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N25" s="14" t="str">
+        <x:v>SRC_V1251_009</x:v>
+      </x:c>
+      <x:c r="O25" s="14" t="str">
+        <x:v>Corporate finance signal tied to fleet scale and charter book.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>2026-06-02</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>AD Ports Group agrees AED 3.1bn acquisition of Brazilian agri-bulk terminal operator CLI</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/06/02/ad-ports-group-acquires-cli</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="str">
+        <x:v>AD Ports agreed to acquire CLI from Macquarie Asset Management and IG4 Capital; CLI operates terminals at Santos and Itaqui.</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str">
+        <x:v>Latin America / Middle East</x:v>
+      </x:c>
+      <x:c r="H26" s="14" t="str">
+        <x:v>Brazil / UAE</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>Ports / Infrastructure / M&amp;A</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="str">
+        <x:v>Transaction</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="str">
+        <x:v>Acquisition pending</x:v>
+      </x:c>
+      <x:c r="L26" s="14" t="str"/>
+      <x:c r="M26" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N26" s="14" t="str">
+        <x:v>SRC_V1251_005</x:v>
+      </x:c>
+      <x:c r="O26" s="14" t="str">
+        <x:v>Links buyer, sellers, CLI and both terminal gateways.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>NEWSV1251_06</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>Macquarie Asset Management-led consortium completes acquisition of Qube</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>Macquarie Group</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>https://www.macquarie.com/li/en/about/news/2026/macquarie-asset-management-led-consortium-announces-successful-completion-of-qube-investment.html</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>A Macquarie Asset Management-led consortium completed the A$11.7bn acquisition of Qube.</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str">
+        <x:v>Asia Pacific</x:v>
+      </x:c>
+      <x:c r="H27" s="14" t="str">
+        <x:v>Australia</x:v>
+      </x:c>
+      <x:c r="I27" s="14" t="str">
+        <x:v>Infrastructure / Logistics / M&amp;A</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="str">
+        <x:v>Transaction</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="str">
+        <x:v>Acquisition completed</x:v>
+      </x:c>
+      <x:c r="L27" s="14" t="str"/>
+      <x:c r="M27" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N27" s="14" t="str">
+        <x:v>SRC_V1251_010</x:v>
+      </x:c>
+      <x:c r="O27" s="14" t="str">
+        <x:v>Capital ownership linked to multimodal infrastructure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>NEWSV1251_07</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>2026-03-30</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>AD Ports publishes 2025 annual report after record revenue and profit</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>https://wpvip.adportsgroup.com/adportsgroup/news-and-media/2026/03/30/ad-ports-group-publishes-2025-annual-report/</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="str">
+        <x:v>AD Ports published its 2025 annual report detailing record performance and corridor expansion.</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="H28" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="str">
+        <x:v>Corporate / Financial</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="str">
+        <x:v>Corporate reporting</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="str">
+        <x:v>Annual report</x:v>
+      </x:c>
+      <x:c r="L28" s="14" t="str"/>
+      <x:c r="M28" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N28" s="14" t="str">
+        <x:v>SRC_V1251_011</x:v>
+      </x:c>
+      <x:c r="O28" s="14" t="str">
+        <x:v>Connects corporate reporting to operating and market metrics.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6184,6 +6496,500 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H48" s="14"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="14" t="str">
+        <x:v>NLINKV1251_001</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>NEWSV1251_01</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>COMP_DAVIE</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H49" s="14" t="str">
+        <x:v>Davie contract award</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="14" t="str">
+        <x:v>NLINKV1251_002</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>NEWSV1251_01</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>PARENT</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H50" s="14" t="str">
+        <x:v>Inocea parent group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="14" t="str">
+        <x:v>NLINKV1251_003</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>NEWSV1251_02</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="str">
+        <x:v>BUYER</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H51" s="14" t="str">
+        <x:v>U.S. acquisition vehicle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="14" t="str">
+        <x:v>NLINKV1251_004</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>NEWSV1251_02</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>COMP_GULF_COPPER</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>TARGET / ASSET</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H52" s="14" t="str">
+        <x:v>Texas shipyard group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="14" t="str">
+        <x:v>NLINKV1251_005</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>NEWSV1251_02</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>COMP_INOCEA</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>PARENT</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H53" s="14" t="str">
+        <x:v>Parent group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="14" t="str">
+        <x:v>NLINKV1251_006</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>NEWSV1251_03</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str">
+        <x:v>Fleet owner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="14" t="str">
+        <x:v>NLINKV1251_007</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>NEWSV1251_03</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>COMP_MAERSK</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>CHARTER PARTNER</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="str">
+        <x:v>Charterer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="14" t="str">
+        <x:v>NLINKV1251_008</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>NEWSV1251_04</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>COMP_SEASPAN_CORP</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="str">
+        <x:v>Rating action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="14" t="str">
+        <x:v>NLINKV1251_009</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>BUYER</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="str">
+        <x:v>Acquirer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="14" t="str">
+        <x:v>NLINKV1251_010</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>COMP_CLI</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>TARGET</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="str">
+        <x:v>Target</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="14" t="str">
+        <x:v>NLINKV1251_011</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>COMP_MACQUARIE_AM</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>SELLER / OWNER</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str">
+        <x:v>Seller / investor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="14" t="str">
+        <x:v>NLINKV1251_012</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>COMP_IG4</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>SELLER / OWNER</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G60" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H60" s="14" t="str">
+        <x:v>Seller / investor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="14" t="str">
+        <x:v>NLINKV1251_013</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>COMP_CLI_NORTE</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>SUBSIDIARY</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="str">
+        <x:v>Itaqui operator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="14" t="str">
+        <x:v>NLINKV1251_014</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>COMP_CLI_SUL</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str">
+        <x:v>SUBSIDIARY</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H62" s="14" t="str">
+        <x:v>Santos operator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>NLINKV1251_015</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>PORTV1251_ITAQUI</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str">
+        <x:v>ASSET LOCATION</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H63" s="14" t="str">
+        <x:v>Itaqui gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>NLINKV1251_016</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>NEWSV1251_05</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>PORTG0049</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>ASSET LOCATION</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str">
+        <x:v>Santos gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>NLINKV1251_017</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>NEWSV1251_06</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>COMP_MACQUARIE_AM</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>CONSORTIUM LEAD</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str">
+        <x:v>Buyer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>NLINKV1251_018</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>NEWSV1251_06</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>COMP_QUBE</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="str">
+        <x:v>TARGET</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H66" s="14" t="str">
+        <x:v>Multimodal target</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>NLINKV1251_019</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>NEWSV1251_07</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G67" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H67" s="14" t="str">
+        <x:v>Annual report</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R94393acfbe0841cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R8e93b041c858461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Rb3ffbb620a9540c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R73f499c8f11240d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rad9bb8cab28540f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R8500a64b32484738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R8ffeb3d22d924c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R6b4728aefb824f18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rba43826fd3aa4e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R3ecb93f54df846ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="Rddc3439a35b34dfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R0dcbdb0726fe4670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R0ea1770d2ff14d6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R1e074750e0274725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R05188ad903764bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Red6f99a5301f48f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Ra9ff8c0c64554772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R42abae39cb6842ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R4e847798d9354cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R6eee331c71be4092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R54dcf2f3ae5d468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rd5d9ad7977f54ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rb816cdaef82941c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R767d0e8143264f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R76acb4136aac4489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R17f656ae97834b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Raa29a634446b4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R981c2615ff8a4a52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5296,6 +5296,321 @@
         <x:v>Connects corporate reporting to operating and market metrics.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>2025-06-03</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>AD Ports inaugurates Tbilisi Intermodal Hub</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2025/06/03/ad-ports-group-inaugurates-tbilisi-intermodal-hub-in-georgia</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>Hub links Georgian rail with Poti and Batumi; first phase includes three 600m rail spurs and a 50,000 sqm container yard.</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>Middle Corridor</x:v>
+      </x:c>
+      <x:c r="H29" s="14" t="str">
+        <x:v>Georgia</x:v>
+      </x:c>
+      <x:c r="I29" s="14" t="str">
+        <x:v>Rail / Inland Logistics</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="str">
+        <x:v>Infrastructure / project</x:v>
+      </x:c>
+      <x:c r="K29" s="14" t="str">
+        <x:v>Hub inauguration</x:v>
+      </x:c>
+      <x:c r="L29" s="14" t="str"/>
+      <x:c r="M29" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N29" s="14" t="str">
+        <x:v>SRC126_001</x:v>
+      </x:c>
+      <x:c r="O29" s="14" t="str">
+        <x:v>System seed for AD Ports / Georgia / Black Sea traversal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>NEWS126_002</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>2026-04-14</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>AD Ports explores investment opportunities at Port of Constanța</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>AD Ports Group</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/04/14/ad-ports-group-signs-agreement-to-explore-investment-opportunities-in-the-port-of-constanta</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>Framework agreement links AD Ports' Middle Corridor strategy to a Black Sea hub connected to rail, road, river and sea networks.</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str">
+        <x:v>Black Sea / Europe</x:v>
+      </x:c>
+      <x:c r="H30" s="14" t="str">
+        <x:v>Romania</x:v>
+      </x:c>
+      <x:c r="I30" s="14" t="str">
+        <x:v>Ports / Infrastructure</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="str">
+        <x:v>Investment / framework</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="str">
+        <x:v>Strategic development</x:v>
+      </x:c>
+      <x:c r="L30" s="14" t="str"/>
+      <x:c r="M30" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N30" s="14" t="str">
+        <x:v>SRC126_002</x:v>
+      </x:c>
+      <x:c r="O30" s="14" t="str">
+        <x:v>Links AD Ports, Constanța, Black Sea, Danube and Middle Corridor.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>NEWS126_003</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>2025-11-28</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>Container Exchange Route provides shared terminal connectivity on Maasvlakte</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>Port of Rotterdam Authority</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>https://www.portofrotterdam.com/en/news-and-press-releases/the-port-of-rotterdam-authority-officially-commissions-container-exchange</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>The 17 km closed road system links major Maasvlakte terminals, depots and customs inspection infrastructure.</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="H31" s="14" t="str">
+        <x:v>Netherlands</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>Ports / Logistics</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="str">
+        <x:v>Infrastructure</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="str">
+        <x:v>Shared port infrastructure</x:v>
+      </x:c>
+      <x:c r="L31" s="14" t="str"/>
+      <x:c r="M31" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N31" s="14" t="str">
+        <x:v>SRC126_004</x:v>
+      </x:c>
+      <x:c r="O31" s="14" t="str">
+        <x:v>Stress-test shared infrastructure linking multiple terminal operators.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>NEWS126_004</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>2026-01-13</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>SIPG highlights Shanghai hub and integrated port-logistics development</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>SIPG</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>https://en.portshanghai.com.cn/LatestNews/4950.jhtml</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>Shanghai's integrated port model combines terminal operations, logistics, investment and Yangtze hinterland connectivity.</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H32" s="14" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="str">
+        <x:v>Ports / Logistics</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="str">
+        <x:v>Corporate / operating model</x:v>
+      </x:c>
+      <x:c r="K32" s="14" t="str">
+        <x:v>Port system</x:v>
+      </x:c>
+      <x:c r="L32" s="14" t="str"/>
+      <x:c r="M32" s="14" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N32" s="14" t="str">
+        <x:v>SRC126_007</x:v>
+      </x:c>
+      <x:c r="O32" s="14" t="str">
+        <x:v>Stress-test listed port group + port area + waterway links.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>NEWS126_005</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>Great Lakes–St. Lawrence lock and canal system retained as one trade system</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>P&amp;C Model Seed</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>https://greatlakes-seaway.com/en/the-seaway/our-locks-and-channels/</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>The stress-test connects Great Lakes ports with the Seaway, Welland Canal, Soo Locks and Atlantic gateway logic.</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H33" s="14" t="str">
+        <x:v>Canada / United States</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>Inland Waterways / Maritime</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="str">
+        <x:v>Model / infrastructure</x:v>
+      </x:c>
+      <x:c r="K33" s="14" t="str">
+        <x:v>System relationship</x:v>
+      </x:c>
+      <x:c r="L33" s="14" t="str"/>
+      <x:c r="M33" s="14" t="str">
+        <x:v>Primary-source model seed</x:v>
+      </x:c>
+      <x:c r="N33" s="14" t="str">
+        <x:v>SRC126_015</x:v>
+      </x:c>
+      <x:c r="O33" s="14" t="str">
+        <x:v>Internal stress-test record backed by official system data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>NEWS126_006</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>Mississippi system modeled as river, locks, ports and intermodal facilities</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>P&amp;C Model Seed</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>https://www.usace.army.mil/Missions/Civil-Works/Navigation-Locks/</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str">
+        <x:v>The stress-test treats navigation locks, river segments, river ports and Gulf export gateways as one connected system.</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H34" s="14" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="I34" s="14" t="str">
+        <x:v>Inland Waterways / Ports</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="str">
+        <x:v>Model / infrastructure</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="str">
+        <x:v>System relationship</x:v>
+      </x:c>
+      <x:c r="L34" s="14" t="str"/>
+      <x:c r="M34" s="14" t="str">
+        <x:v>Primary-source model seed</x:v>
+      </x:c>
+      <x:c r="N34" s="14" t="str">
+        <x:v>SRC126_014</x:v>
+      </x:c>
+      <x:c r="O34" s="14" t="str">
+        <x:v>Internal stress-test record backed by USACE data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>Genoa pushes ahead with megaship access expansion</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>https://splash247.com/genoa-pushes-ahead-with-megaship-access-expansion/</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str">
+        <x:v>Genoa's new offshore breakwater entered a new construction phase with crest-wall work and the 32nd caisson, supporting wider access for latest-generation containerships and reinforcing the port's rail-hinterland strategy.</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="H35" s="14" t="str">
+        <x:v>Italy</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>Ports / Rail / Infrastructure</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="str">
+        <x:v>Infrastructure / project</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="str">
+        <x:v>Megaship access / breakwater</x:v>
+      </x:c>
+      <x:c r="L35" s="14" t="str"/>
+      <x:c r="M35" s="14" t="str">
+        <x:v>Reported; primary-source confirmation</x:v>
+      </x:c>
+      <x:c r="N35" s="14" t="str">
+        <x:v>SRC1261_004</x:v>
+      </x:c>
+      <x:c r="O35" s="14" t="str">
+        <x:v>Links marine access, port governance, construction consortium, megaship capability and Rhine-Alpine rail connectivity.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6989,6 +7304,630 @@
       </x:c>
       <x:c r="H67" s="14" t="str">
         <x:v>Annual report</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>NL126_001</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G68" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H68" s="14" t="str">
+        <x:v>Investor / owner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>NL126_002</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>ASSET_TBILISI</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>ASSET</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G69" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H69" s="14" t="str">
+        <x:v>Tbilisi hub</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>NL126_003</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>COMP_GEORGIAN_RAILWAY</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>RAIL CONNECTION</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G70" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H70" s="14" t="str">
+        <x:v>National rail</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>NL126_004</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>PORT_POTI</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>GATEWAY</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H71" s="14" t="str">
+        <x:v>Black Sea port</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>NL126_005</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>NEWS126_001</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>PORT_BATUMI</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>GATEWAY</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G72" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H72" s="14" t="str">
+        <x:v>Black Sea port</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>NL126_006</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>NEWS126_002</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>COMP_ADPORTS</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str">
+        <x:v>Investor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>NL126_007</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>NEWS126_002</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>PORT_CONSTANTA</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>TARGET / GATEWAY</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G74" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H74" s="14" t="str">
+        <x:v>Black Sea / Danube port</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>NL126_008</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>NEWS126_003</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>PORT_ROTTERDAM</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G75" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H75" s="14" t="str">
+        <x:v>Port system</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>NL126_009</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>NEWS126_003</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>ASSET_CER</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G76" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="str">
+        <x:v>Shared infrastructure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>NL126_010</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>NEWS126_004</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>COMP_SIPG</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H77" s="14" t="str">
+        <x:v>Integrated port group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>NL126_011</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>NEWS126_004</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>PORT_SHANGHAI</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>PORT SYSTEM</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G78" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H78" s="14" t="str">
+        <x:v>Port of Shanghai</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>NL126_012</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>NEWS126_004</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>WATER_YANGTZE</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>HINTERLAND WATERWAY</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G79" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str">
+        <x:v>Yangtze</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>NL126_013</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>NEWS126_005</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>WATER_GLSS</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>SYSTEM</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H80" s="14" t="str">
+        <x:v>Great Lakes–St. Lawrence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>NL126_014</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>NEWS126_005</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>CANAL_WELLAND</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>FACILITY</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str">
+        <x:v>Welland Canal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>NL126_015</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>NEWS126_005</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>LOCK_SOO</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>FACILITY</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H82" s="14" t="str">
+        <x:v>Soo Locks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>NL126_016</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>NEWS126_006</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>WATER_MISS</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E83" s="14" t="str">
+        <x:v>SYSTEM</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G83" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H83" s="14" t="str">
+        <x:v>Mississippi system</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>NL126_017</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>NEWS126_006</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>PORT_SOUTH_LA</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>System Entity</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>PORT</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H84" s="14" t="str">
+        <x:v>Lower Mississippi gateway</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>NL1261_001</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>COMP_WLSPA</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>COMMISSIONING AUTHORITY</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H85" s="14" t="str">
+        <x:v>Western Ligurian Sea Port Authority</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
+        <x:v>NL1261_002</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>PORT_GENOA</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>LOCATION / BENEFICIARY</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G86" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H86" s="14" t="str">
+        <x:v>Port of Genoa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>NL1261_003</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>ASSET_GENOA_BREAKWATER</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>Asset</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H87" s="14" t="str">
+        <x:v>New Genoa Breakwater</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="14" t="str">
+        <x:v>NL1261_004</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>COMP_PERGENOVA</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>CONTRACTOR</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G88" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H88" s="14" t="str">
+        <x:v>Construction consortium</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="14" t="str">
+        <x:v>NL1261_005</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>COMP_WEBUILD</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>CONSORTIUM LEAD</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str">
+        <x:v>Webuild</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="14" t="str">
+        <x:v>NL1261_006</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>ASSET_TERZO_VALICO</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>Asset</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>RELATED RAIL PROJECT</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G90" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H90" s="14" t="str">
+        <x:v>Port-hinterland rail</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="14" t="str">
+        <x:v>NL1261_007</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>NEWS1261_001</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>CORR_RHINE_ALPINE</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>Corridor</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>CORRIDOR</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H91" s="14" t="str">
+        <x:v>TEN-T Rhine-Alpine corridor</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R05188ad903764bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Red6f99a5301f48f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Ra9ff8c0c64554772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R42abae39cb6842ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R4e847798d9354cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R6eee331c71be4092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R54dcf2f3ae5d468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rd5d9ad7977f54ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rb816cdaef82941c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R767d0e8143264f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R76acb4136aac4489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R17f656ae97834b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Raa29a634446b4488"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R981c2615ff8a4a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6642d6f68cf74859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R7f4a990a922c4a8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R1cccd52fd6524fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rd6c44f3870b14e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Ra9df8da01d0f48b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rb0223ca2513a4656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Reaa086cd38c748d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R8d35e888f71f4eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf11aa99a25104c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="Rb3087eb3d9df498b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R71bb75e7494d410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R3eb54e6a0ee54d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rd85b9f86fb7e44a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R712c193f0cf24c54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5611,6 +5611,98 @@
         <x:v>Links marine access, port governance, construction consortium, megaship capability and Rhine-Alpine rail connectivity.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>NEWS130_001</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>2026-09-07</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Sanctioned Russian-flagged LADY MARIIA reportedly struck by aerial drones in central Mediterranean</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Power &amp; Corridors</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>https://www.powerncorridors.com/maritime-alert-central-mediterranean-crete-libya-07-sept-2026/</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>LADY MARIIA (IMO 9220641) was reportedly struck between Crete and Libya; fires were visible after multiple impacts and responsibility remained unconfirmed.</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Mediterranean</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>International waters</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Maritime Security / Sanctions</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Security incident</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>Aerial drone attack</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>EVENT130_001</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>Reported / attribution unconfirmed</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>SRC130_006</x:v>
+      </x:c>
+      <x:c r="O36" t="str">
+        <x:v>Canonical vessel + sanctions + incident integration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>NEWS130_002</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>EUNAVFOR MED IRINI boards sanctioned tanker SUN for flag verification</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>USNI News</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>https://news.usni.org/2026/09/02/european-union-naval-force-intercepts-suspected-russian-shadow-fleet-tanker</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>IRINI forces boarded SUN (IMO 9293117) on 30 Aug 2026 in the Mediterranean amid suspected false-flag / shadow-fleet concerns.</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Mediterranean</x:v>
+      </x:c>
+      <x:c r="H37"/>
+      <x:c r="I37" t="str">
+        <x:v>Maritime Enforcement / Sanctions</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>Boarding / enforcement</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>Flag verification</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>EVENT130_002</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>Reported / official operation cited</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>SRC130_007</x:v>
+      </x:c>
+      <x:c r="O37" t="str">
+        <x:v>Canonical vessel + sanctions + enforcement integration.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7906,28 +7998,106 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="14" t="str">
-        <x:v>NL1261_007</x:v>
+        <x:v>NL130_001</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>NEWS1261_001</x:v>
+        <x:v>NEWS130_001</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>CORR_RHINE_ALPINE</x:v>
+        <x:v>VESSEL_SAN_001</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>Corridor</x:v>
+        <x:v>Vessel</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
-        <x:v>CORRIDOR</x:v>
+        <x:v>SUBJECT</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>Secondary</x:v>
+        <x:v>Primary</x:v>
       </x:c>
       <x:c r="G91" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H91" s="14" t="str">
-        <x:v>TEN-T Rhine-Alpine corridor</x:v>
+        <x:v>LADY MARIIA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>NL130_002</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>NEWS130_001</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>COMP_MG_FLOT</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>OWNER / MANAGER</x:v>
+      </x:c>
+      <x:c r="F92" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G92" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H92" t="str">
+        <x:v>MG-FLOT LLC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>NL130_003</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>NEWS130_002</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>VESSEL_SAN_002</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F93" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G93" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H93" t="str">
+        <x:v>SUN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>NL130_004</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>NEWS130_002</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>COMP_WAVEWHISPER</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>OWNER / OPERATOR</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G94" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>Wavewhisper Shipping Ltd</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8557,6 +8727,70 @@
       </x:c>
       <x:c r="J19" s="14" t="str">
         <x:v>SRC_0345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>EVENT130_001</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Security incident / vessel attack</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>VESSEL_SAN_001</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Central Mediterranean / Crete–Libya</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>LADY MARIIA reportedly struck by aerial drones</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Multiple aerial drone impacts were reported on the sanctioned Russian-flagged ro-ro while sailing east after departing Oran.</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Fire and damage reported; AIS reporting became stale after the incident.</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>Extends Russia-linked vessel targeting into the central Mediterranean and raises sanctions/security exposure.</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>SRC130_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>EVENT130_002</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>2026-08-30</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Maritime enforcement / boarding</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>VESSEL_SAN_002</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Mediterranean / south of Sicily</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>IRINI boards SUN for flag verification</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>EUNAVFOR MED IRINI forces boarded the sanctioned tanker SUN to verify its flag amid suspected false-flag and shadow-fleet activity.</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Boarding / inspection; operational outcome not publicly detailed in cited reporting.</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Illustrates growing enforcement pressure on sanctioned Russia-linked tanker networks.</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>SRC130_007</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6642d6f68cf74859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R7f4a990a922c4a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R1cccd52fd6524fbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rd6c44f3870b14e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Ra9df8da01d0f48b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rb0223ca2513a4656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Reaa086cd38c748d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R8d35e888f71f4eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf11aa99a25104c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="Rb3087eb3d9df498b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R71bb75e7494d410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R3eb54e6a0ee54d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rd85b9f86fb7e44a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R712c193f0cf24c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R3e294904853b4444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R68fd75bc95a843aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R8b3ff927bdb04c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rb4f3d5fe51704d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rbcb9f151a32d4ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R8aff96186b014ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R31d5b2cbf772443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rcc0c3cf7c0744c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R086dc8c413a24197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R9a8ca29473b04b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R7fbe8ac5747241f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Rc5fdfb6903b64709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rce3f8f21740e45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Re8366ceccd2d4bdf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5703,6 +5703,194 @@
         <x:v>Canonical vessel + sanctions + enforcement integration.</x:v>
       </x:c>
     </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>CENTCOM strikes five Iran-linked tankers in Gulf of Oman and near Kharg Island</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>U.S. Central Command</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>https://www.centcom.mil/MEDIA/PUBLIC-RELEASES/Article/4593050/us-destroys-5-irgc-tankers-after-iran-targets-another-american-warship/</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>CENTCOM said it destroyed RIESCO, HORIZON 1, KAVIZ and CHARMINAR in the Gulf of Oman and DERYA near Kharg Island after attempted IRGC ballistic-missile attacks on a U.S. warship; crews were told to abandon ship.</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Persian Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Iran / international waters</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Maritime Security / Energy</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>Kinetic strike</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>US military strike on tankers</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Official CENTCOM statement</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>Five canonical tanker objects linked.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>NEWS132_002</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>NEW ANDROS hit by drone in Iraqi territorial waters</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Panama-flagged NEW ANDROS, carrying about 2 million barrels of Iraqi fuel oil and used as floating storage, was struck by a drone in Iraqi waters; 22 crew were safe and no cargo leakage was reported.</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Northern Persian Gulf</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Iraq</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>Maritime Security / Energy</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>Drone strike</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Commercial tanker attack</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>EVENT132_002</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Reported by Reuters / Iraqi officials</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>Canonical vessel + charter/storage exposure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>NEWS132_003</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Unidentified tanker reported listing 24 nm northwest of Port Rashid</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Reuters / UKMTO</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>UKMTO reported an unidentified vessel listing while at anchor 24 nautical miles northwest of Port Rashid, possibly after water ingress following an attack by an unknown projectile.</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Dubai / Persian Gulf</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Maritime Security</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>Projectile / water ingress</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Unidentified tanker incident</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>EVENT132_003</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>Vessel identity unconfirmed</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>Do not create a vessel record until identity is confirmed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>NEWS132_004</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Merchant-vessel attacks expand across Gulf as Iran claims strikes on 10 ships</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>https://www.reuters.com/world/europe/several-merchant-vessels-hit-by-disabling-fire-gulf-gulf-oman-2026-09-09/</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Iran said it had attacked 10 ships near the Strait of Hormuz after U.S. strikes on five Iran-linked tankers; UKMTO reported several merchant vessels hit by disabling fire in the northern Gulf and Gulf of Oman.</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Strait of Hormuz / Persian Gulf / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Maritime Security / Trade</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>Regional escalation</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Multiple merchant-vessel attacks</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>Claims and incident reporting remain partly unverified at vessel level</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>Regional umbrella event for linked commercial-shipping incidents.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8098,6 +8286,266 @@
       </x:c>
       <x:c r="H94" t="str">
         <x:v>Wavewhisper Shipping Ltd</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>NL132_001</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G95" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>RIESCO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>NL132_002</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>VES_GULF_HORIZON1</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>HORIZON 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>NL132_003</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>VES_GULF_KAVIZ</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>KAVIZ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>NL132_004</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>CHARMINAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>NL132_005</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>NEWS132_001</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>DERYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>NL132_006</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>NEWS132_002</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>NEW ANDROS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>NL132_007</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>NEWS132_002</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>CHARTERER / STORAGE USER</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>Iraqi Oil Tankers Company</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>NL132_008</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>NEWS132_002</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>COMP_INVINCIBLE_SHIPPING</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>REGISTERED OWNER</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>Invincible Shipping Services Inc.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>NL132_009</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>NEWS132_002</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>COMP_NEW_SHIPPING</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>MANAGEMENT COMPANY</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>New Shipping Limited</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>NL132_010</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>NEWS132_004</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>REGIONAL SECURITY SYSTEM</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8791,6 +9239,134 @@
       </x:c>
       <x:c r="J21" t="str">
         <x:v>SRC130_007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Kinetic strike / tanker interdiction</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Gulf of Oman / Kharg Island</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>CENTCOM strikes five Iran-linked tankers</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>U.S. forces struck RIESCO, HORIZON 1, KAVIZ, CHARMINAR and DERYA; CENTCOM said crews were warned to abandon ship and the vessels were rendered inoperable.</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Five tanker hulls removed from service; RIESCO reported sunk.</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Direct targeting of tanker mobility and Iran-linked oil-network capacity raises commercial-war-risk and shadow-fleet exposure across the Gulf.</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>EVENT132_002</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Drone attack on commercial tanker</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Iraqi territorial waters / southeast of Al-Faw</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>NEW ANDROS hit by drone</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>NEW ANDROS was struck by an unknown-source drone while laden with Iraqi fuel oil and used as floating storage.</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Minor hull damage / onboard fire reported; crew safe; no leakage reported.</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Shows commercial tanker exposure extending beyond Hormuz into Iraqi Gulf waters and floating-storage operations.</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>EVENT132_003</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Projectile attack / water ingress</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>PORTG0045</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>24 nm northwest of Mina Rashid / Port Rashid</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Unidentified tanker reported listing near Dubai</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>UKMTO reporting cited by Reuters described an anchored vessel listing, possibly after water ingress from an unknown projectile.</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>Potential flooding / casualty response; identity unconfirmed.</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>Raises anchorage and bunkering risk around Dubai / UAE Gulf waters.</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Regional maritime escalation</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Persian Gulf / Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Iran claims attacks on 10 ships amid broader merchant-vessel strikes</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Iran claimed attacks on 10 ships near the Strait of Hormuz while UKMTO reported several merchant vessels hit by disabling fire.</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Multiple commercial vessels affected; exact vessel-level attribution remains incomplete.</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>War-risk pricing, route avoidance, bunkering disruption and reduced Hormuz throughput become system-level concerns.</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>SRC132_003</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -51220,6 +51796,314 @@
         <x:v>Yeosu-Gwangyang PA</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>EL132_001</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>VES_GULF_RIESCO</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>CENTCOM strike / sunk reported</x:v>
+      </x:c>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>EL132_002</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>VES_GULF_HORIZON1</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>EL132_003</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>VES_GULF_KAVIZ</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+      <x:c r="I31"/>
+      <x:c r="J31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>EL132_004</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>VES_GULF_CHARMINAR</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>CENTCOM strike / rendered inoperable</x:v>
+      </x:c>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>EL132_005</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>VES_GULF_DERYA</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>CENTCOM strike near Kharg</x:v>
+      </x:c>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>EL132_006</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>EVENT132_002</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>VES_GULF_NEW_ANDROS</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>DIRECTLY_AFFECTED</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Drone strike / minor damage</x:v>
+      </x:c>
+      <x:c r="I34"/>
+      <x:c r="J34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>EL132_007</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EVENT132_002</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>COMP_IOTC</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>CHARTERER_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Charter / floating-storage exposure</x:v>
+      </x:c>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>EL132_008</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>EVENT132_003</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>PORTG0045</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>NEARBY_ANCHORAGE_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>24 nm northwest of Port Rashid / Mina Rashid</x:v>
+      </x:c>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>EL132_009</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>System</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>DIRECT_SYSTEM_IMPACT</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Regional escalation</x:v>
+      </x:c>
+      <x:c r="I37"/>
+      <x:c r="J37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>EL132_010</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>PORTG0046</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>BUNKERING / GATEWAY EXPOSURE</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Fujairah exposure in wider Gulf of Oman security environment</x:v>
+      </x:c>
+      <x:c r="I38"/>
+      <x:c r="J38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>EL132_011</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>PORTG0250</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>NORTHERN_GULF_EXPOSURE</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Basra / Iraqi Gulf gateway exposure</x:v>
+      </x:c>
+      <x:c r="I39"/>
+      <x:c r="J39"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -52137,6 +53021,198 @@
         <x:v>Localized friction at the UK's main cross-Channel ferry gateway; no confirmed prolonged port shutdown</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>IMP132_001</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Operational</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Tanker mobility / hull availability</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Five vessels removed from normal operation</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>CENTCOM statement / Reuters</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>SRC132_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>IMP132_002</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>EVENT132_001</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Commercial</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Secondary</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>War-risk / shadow fleet</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Iran-linked tanker operations face higher kinetic and compliance exposure</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Immediate / ongoing</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Analytical assessment</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>SRC132_002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>IMP132_003</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>EVENT132_002</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Operational</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Floating storage / tanker operations</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>NEW ANDROS damaged while storing Iraqi fuel oil</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Reuters / Iraqi Oil Ministry</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>IMP132_004</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>EVENT132_003</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Operational</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Dubai anchorage safety</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Unidentified tanker listing / water ingress</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Medium-High</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>UKMTO via Reuters</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>IMP132_005</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Commercial</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Systemic</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>War-risk premiums / routing</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Higher risk pricing and route avoidance across Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Analytical assessment from current attack pattern</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>IMP132_006</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>EVENT132_004</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Trade</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Systemic</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>Energy / bunkering / transit throughput</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Fujairah/Khor Fakkan and Hormuz traffic face disruption and reduced confidence</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Reuters traffic / incident reporting</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>SRC132_003</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R3e294904853b4444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R68fd75bc95a843aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R8b3ff927bdb04c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rb4f3d5fe51704d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rbcb9f151a32d4ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R8aff96186b014ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R31d5b2cbf772443c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rcc0c3cf7c0744c44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R086dc8c413a24197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R9a8ca29473b04b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R7fbe8ac5747241f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Rc5fdfb6903b64709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rce3f8f21740e45d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Re8366ceccd2d4bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R568a6ba1c0464514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R8114bb2e83b149e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R8bf804b54a2140d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R148b2db936e245f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rcf3e75c1e0d5411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R27a055e4d22d467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R1a9e6c6b74114373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rf774ebf6c36b4c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf46fc96d32824804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R8882315a58b547fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R115c7e5b0a534f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R0a0542b1e7c44fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R206f1e3e31d6448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R8dfe9cbb3af74714"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5891,6 +5891,145 @@
         <x:v>Regional umbrella event for linked commercial-shipping incidents.</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>NEWS133_001</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Peninsula confirms tanker involved in incident off Dubai</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>One crewmember died and another was missing after an incident involving HERCULES STAR at anchorage off Dubai; all other crew were accounted for.</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Persian Gulf</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Maritime security / bunker supply</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Vessel casualty</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Suspected projectile / taking water</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>Company-confirmed casualty; attack mechanism not fully resolved</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>Keep separate from March 2026 HERCULES STAR incident.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>NEWS133_002</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Nisg̱a'a, Tahltan Nations mark official opening of Stewart, B.C., port as expansion plans take shape</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>CBC News</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Official port opening and expansion-planning milestone involving the Nisg̱a'a and Tahltan Nations.</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Ports / infrastructure</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>Port opening</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Expansion planning</x:v>
+      </x:c>
+      <x:c r="L43" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Headline verified; article detail access-limited</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>Do not infer ownership, operator or capacity from headline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>NEWS133_003</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Cruise operators reap benefits of their own private islands</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Reuters</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>Private destinations are reshaping cruise investment, revenue capture and Caribbean call patterns.</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Caribbean</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Regional</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Cruise / tourism</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Strategic investment</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Private destination expansion</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>EVT133_003</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>SRC133_003</x:v>
+      </x:c>
+      <x:c r="O44" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8547,6 +8686,224 @@
       <x:c r="H104" t="str">
         <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
       </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>NL133_001</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>NEWS133_001</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>VES_HERCULES_STAR</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H105" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>NL133_002</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>NEWS133_001</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>COMP_PENINSULA</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>CHARTERER</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H106" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>NL133_003</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>NEWS133_001</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>COMP_HERCULES_TANKER</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>SISTER COMPANY / VESSEL PROVIDER</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H107" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>NL133_004</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>NEWS133_002</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>OPENED PORT</x:v>
+      </x:c>
+      <x:c r="F108" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G108" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>Headline-level record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>NL133_005</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>NEWS133_002</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>ORG_NISGAA_NATION</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>Organization</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>OPENING PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F109" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G109" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H109" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>NL133_006</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>NEWS133_002</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>ORG_TAHLTAN_NATION</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>Organization</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>OPENING PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F110" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G110" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H110" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>NL133_007</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>NEWS133_003</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>SECTOR PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F111" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G111" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H111" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>NL133_008</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>NEWS133_003</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>COMP_CARNIVAL_CORP</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>SECTOR PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F112" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G112" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H112" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>NL133_009</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>NEWS133_003</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>COMP_NCLH</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>SECTOR PARTICIPANT</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H113" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50891,6 +51248,170 @@
         <x:v>Implementation status should be checked against primary Korean government sources before canonical ownership/governance overwrite.</x:v>
       </x:c>
     </x:row>
+    <x:row r="613">
+      <x:c r="A613" t="str">
+        <x:v>OBS_000612</x:v>
+      </x:c>
+      <x:c r="B613" t="str">
+        <x:v>EVT133_001</x:v>
+      </x:c>
+      <x:c r="C613" t="str">
+        <x:v>news_intake_v1_33</x:v>
+      </x:c>
+      <x:c r="D613" t="str">
+        <x:v>NEWS133_001</x:v>
+      </x:c>
+      <x:c r="E613" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="F613" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="G613" t="str">
+        <x:v>Vessel incident</x:v>
+      </x:c>
+      <x:c r="H613" t="str">
+        <x:v>Suspected projectile / taking water report</x:v>
+      </x:c>
+      <x:c r="I613" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J613" t="str">
+        <x:v>Persian Gulf</x:v>
+      </x:c>
+      <x:c r="K613" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
+      <x:c r="L613" t="str">
+        <x:v>Anchorage off Dubai</x:v>
+      </x:c>
+      <x:c r="M613" t="str"/>
+      <x:c r="N613" t="str"/>
+      <x:c r="O613" t="str">
+        <x:v>HERCULES STAR</x:v>
+      </x:c>
+      <x:c r="P613" t="str">
+        <x:v>9916135</x:v>
+      </x:c>
+      <x:c r="Q613" t="str">
+        <x:v>Product tanker</x:v>
+      </x:c>
+      <x:c r="R613" t="str">
+        <x:v>Unknown / unconfirmed</x:v>
+      </x:c>
+      <x:c r="S613" t="str">
+        <x:v>Peninsula confirmed a fatal incident involving HERCULES STAR. A nearby UKMTO projectile report was cited but not conclusively matched.</x:v>
+      </x:c>
+      <x:c r="T613" t="str">
+        <x:v>One fatality; one missing; other crew accounted for</x:v>
+      </x:c>
+      <x:c r="U613" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V613" t="str"/>
+      <x:c r="W613" t="str">
+        <x:v>Emergency response and casualty investigation</x:v>
+      </x:c>
+      <x:c r="X613" t="str">
+        <x:v>Bunker tanker / anchorage risk</x:v>
+      </x:c>
+      <x:c r="Y613" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="Z613" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA613" t="str">
+        <x:v>SRC133_001</x:v>
+      </x:c>
+      <x:c r="AB613" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC613" t="str">
+        <x:v>Separate from the 1 Mar 2026 minor-damage observation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614">
+      <x:c r="A614" t="str">
+        <x:v>OBS_000613</x:v>
+      </x:c>
+      <x:c r="B614" t="str">
+        <x:v>EVT133_002</x:v>
+      </x:c>
+      <x:c r="C614" t="str">
+        <x:v>news_intake_v1_33</x:v>
+      </x:c>
+      <x:c r="D614" t="str">
+        <x:v>NEWS133_002</x:v>
+      </x:c>
+      <x:c r="E614" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F614" t="str">
+        <x:v>Infrastructure / Commercial</x:v>
+      </x:c>
+      <x:c r="G614" t="str">
+        <x:v>Port opening</x:v>
+      </x:c>
+      <x:c r="H614" t="str">
+        <x:v>Expansion planning</x:v>
+      </x:c>
+      <x:c r="I614" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="J614" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="K614" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="L614" t="str">
+        <x:v>Stewart, British Columbia</x:v>
+      </x:c>
+      <x:c r="M614" t="str"/>
+      <x:c r="N614" t="str"/>
+      <x:c r="O614" t="str">
+        <x:v>Port of Stewart</x:v>
+      </x:c>
+      <x:c r="P614" t="str">
+        <x:v>PORT_STEWART_BC</x:v>
+      </x:c>
+      <x:c r="Q614" t="str">
+        <x:v>Port / harbour</x:v>
+      </x:c>
+      <x:c r="R614" t="str">
+        <x:v>Nisg̱a'a Nation; Tahltan Nation</x:v>
+      </x:c>
+      <x:c r="S614" t="str">
+        <x:v>Official opening reported with expansion plans taking shape.</x:v>
+      </x:c>
+      <x:c r="T614" t="str">
+        <x:v>New gateway / development milestone</x:v>
+      </x:c>
+      <x:c r="U614" t="str"/>
+      <x:c r="V614" t="str"/>
+      <x:c r="W614" t="str">
+        <x:v>Port opening and planned expansion</x:v>
+      </x:c>
+      <x:c r="X614" t="str">
+        <x:v>Potential northern B.C. trade and project-cargo connectivity</x:v>
+      </x:c>
+      <x:c r="Y614" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="Z614" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="AA614" t="str">
+        <x:v>SRC133_002</x:v>
+      </x:c>
+      <x:c r="AB614" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC614" t="str">
+        <x:v>Headline-level evidence only; verify operator, ownership, cargo and capacity before enrichment.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R568a6ba1c0464514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R8114bb2e83b149e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R8bf804b54a2140d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R148b2db936e245f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rcf3e75c1e0d5411f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R27a055e4d22d467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R1a9e6c6b74114373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rf774ebf6c36b4c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf46fc96d32824804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R8882315a58b547fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R115c7e5b0a534f9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R0a0542b1e7c44fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R206f1e3e31d6448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R8dfe9cbb3af74714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R30db454c71b846b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R72528468526a4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R273618b80968497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R00e84d71528946a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R67025ecbb94c429d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R6b70132e45fa4974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Rdbdade14ce8f48cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rc2b67467b50a40fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf2fb2202758149ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R394cf27e44024963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R76d87421dee34625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R957d0b8292974658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rae86b3fe47494ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Ree4d1af6feab4730"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -847,6 +847,59 @@
         <x:v>Designed for cross-event pattern analysis.</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>MON134_001</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Strait of Hormuz traffic and AIS confidence</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Security / Trade Flow</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Persian Gulf / Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>2026-03-08</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Daily to monthly</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>AIS-derived crossings, direction, tanker movements and estimated oil exports</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Crossings; inbound/outbound balance; outbound oil tankers; estimated oil; ship counts by zone; AIS coverage caveats</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Material traffic recovery/deterioration or change in AIS coverage confidence</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>SYS_HORMUZ_SECURITY</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>SRC134_001</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>Monthly close / 30-minute API refresh</x:v>
+      </x:c>
+      <x:c r="Q7" t="str">
+        <x:v>Counts are conservative lower bounds during wartime jamming; September 2026 is partial.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6030,6 +6083,237 @@
       </x:c>
       <x:c r="O44" t="str"/>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>NEWS134_001</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Oil Tanker Company Says It’s Owed $55 Million in Rate Dispute</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Middle East / Global</x:v>
+      </x:c>
+      <x:c r="H45" t="str"/>
+      <x:c r="I45" t="str">
+        <x:v>Tankers / freight markets</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Commercial / legal dispute</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Rate benchmark / receivable</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Reported / pending adjudication</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Counterparty undisclosed in current article; Mercuria appeared in earlier company reporting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>NEWS134_002</x:v>
+      </x:c>
+      <x:c r="B46" t="str"/>
+      <x:c r="C46" t="str">
+        <x:v>Seaspan awarded a submarine maintenance contract extension by Babcock Canada through 2032</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Seaspan</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Defence shipbuilding / MRO</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>Contract extension</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Submarine maintenance</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>EVT134_002</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Official headline verified; value and announcement date not captured</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>SRC134_004</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>Do not infer contract value or expanded scope beyond the source headline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>MSC Shipmanagement Fined $1.75 Million Over Illegal Oily Waste Discharges</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Shipping / environmental compliance</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Enforcement</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>MARPOL / APPS oily-waste discharge</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Guilty pleas / court order reported</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Vessel identifiers beyond name require registry verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>NEWS134_004</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>U.S. Adds 16 Maritime Training Centers Amid Shipbuilding Push</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>gCaptain</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>North America</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>Maritime workforce / shipbuilding</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>Programme expansion</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>Training-center designations</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>EVT134_004</x:v>
+      </x:c>
+      <x:c r="M48" t="str">
+        <x:v>Reported from MARAD programme information</x:v>
+      </x:c>
+      <x:c r="N48" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="O48" t="str">
+        <x:v>Five institutions named in source captured; full 16-institution roster remains a research item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Russia's Arctic LNG 2 Seeks $1 Billion in Damages From South Korea's Hanwha</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Reuters / gCaptain</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>Arctic / Asia</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Russia / South Korea</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>LNG / shipbuilding</x:v>
+      </x:c>
+      <x:c r="J49" t="str">
+        <x:v>Commercial / legal dispute</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>Shipbuilding arbitration</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="M49" t="str">
+        <x:v>Reported / pending arbitration</x:v>
+      </x:c>
+      <x:c r="N49" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="O49" t="str">
+        <x:v>Sanctions and canceled carrier orders are central context.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8904,6 +9188,296 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H113" t="str"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>NL134_001</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>NEWS134_001</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>CLAIMANT</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H114" t="str"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>NL134_002</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>NEWS134_001</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>COMP_MERCURIA</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>REPORTED EARLIER COUNTERPARTY</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>Context</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>Current article does not disclose the counterparty.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>NL134_003</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>NEWS134_002</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>COMP_SEASPAN_ULC</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>CONTRACTOR</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H116" t="str"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>NL134_004</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>NEWS134_002</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>COMP_BABCOCK_CANADA</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>PRIME CONTRACTOR / CUSTOMER</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H117" t="str"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>NL134_005</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H118" t="str"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>NL134_006</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>DEFENDANT / MANAGER</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H119" t="str"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>NL134_007</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>DEFENDANT / OWNER</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H120" t="str"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>NL134_008</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>ORG_USCG</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>Government agency</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>INVESTIGATOR</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H121" t="str"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>NL134_009</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>NEWS134_004</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>Government agency</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>PROGRAMME OWNER</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H122" t="str"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>NL134_010</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>COMP_ARCTIC_LNG2</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>CLAIMANT</x:v>
+      </x:c>
+      <x:c r="F123" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G123" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H123" t="str"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>NL134_011</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>COMP_HANWHA_OCEAN</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>RESPONDENT</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H124" t="str"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>NL134_012</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>COMP_NOVATEK</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>PROJECT LEAD</x:v>
+      </x:c>
+      <x:c r="F125" t="str">
+        <x:v>Context</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H125" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51412,6 +51986,407 @@
         <x:v>Headline-level evidence only; verify operator, ownership, cargo and capacity before enrichment.</x:v>
       </x:c>
     </x:row>
+    <x:row r="615">
+      <x:c r="A615" t="str">
+        <x:v>OBS_000614</x:v>
+      </x:c>
+      <x:c r="B615" t="str">
+        <x:v>EVT134_001</x:v>
+      </x:c>
+      <x:c r="C615" t="str">
+        <x:v>news_intake_v1_34</x:v>
+      </x:c>
+      <x:c r="D615" t="str">
+        <x:v>NEWS134_001</x:v>
+      </x:c>
+      <x:c r="E615" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F615" t="str">
+        <x:v>Commercial / Legal</x:v>
+      </x:c>
+      <x:c r="G615" t="str">
+        <x:v>Commercial / legal dispute</x:v>
+      </x:c>
+      <x:c r="H615" t="str">
+        <x:v>Rate benchmark / receivable</x:v>
+      </x:c>
+      <x:c r="I615" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J615" t="str">
+        <x:v>Persian Gulf / Global</x:v>
+      </x:c>
+      <x:c r="K615" t="str"/>
+      <x:c r="L615" t="str">
+        <x:v>Tanker rate market</x:v>
+      </x:c>
+      <x:c r="M615" t="str"/>
+      <x:c r="N615" t="str"/>
+      <x:c r="O615" t="str">
+        <x:v>Hunter Group ASA</x:v>
+      </x:c>
+      <x:c r="P615" t="str">
+        <x:v>COMP_HUNTER_GROUP</x:v>
+      </x:c>
+      <x:c r="Q615" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="R615" t="str">
+        <x:v>Hunter Group / undisclosed counterparty</x:v>
+      </x:c>
+      <x:c r="S615" t="str">
+        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
+      </x:c>
+      <x:c r="T615" t="str">
+        <x:v>Pending court dispute</x:v>
+      </x:c>
+      <x:c r="U615" t="str"/>
+      <x:c r="V615" t="str"/>
+      <x:c r="W615" t="str">
+        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
+      </x:c>
+      <x:c r="X615" t="str">
+        <x:v>Tanker rate and receivable risk</x:v>
+      </x:c>
+      <x:c r="Y615" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="Z615" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA615" t="str">
+        <x:v>SRC134_003</x:v>
+      </x:c>
+      <x:c r="AB615" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC615" t="str">
+        <x:v>Counterparty undisclosed in current article; Mercuria appeared in earlier company reporting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616">
+      <x:c r="A616" t="str">
+        <x:v>OBS_000615</x:v>
+      </x:c>
+      <x:c r="B616" t="str">
+        <x:v>EVT134_002</x:v>
+      </x:c>
+      <x:c r="C616" t="str">
+        <x:v>news_intake_v1_34</x:v>
+      </x:c>
+      <x:c r="D616" t="str">
+        <x:v>NEWS134_002</x:v>
+      </x:c>
+      <x:c r="E616" t="str"/>
+      <x:c r="F616" t="str">
+        <x:v>Defence / Industrial</x:v>
+      </x:c>
+      <x:c r="G616" t="str">
+        <x:v>Contract extension</x:v>
+      </x:c>
+      <x:c r="H616" t="str">
+        <x:v>Submarine maintenance</x:v>
+      </x:c>
+      <x:c r="I616" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J616" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="K616" t="str">
+        <x:v>Canada</x:v>
+      </x:c>
+      <x:c r="L616" t="str">
+        <x:v>Victoria, British Columbia</x:v>
+      </x:c>
+      <x:c r="M616" t="str"/>
+      <x:c r="N616" t="str"/>
+      <x:c r="O616" t="str">
+        <x:v>Victoria-class submarine support</x:v>
+      </x:c>
+      <x:c r="P616" t="str">
+        <x:v>PROG_SEA_VISSC</x:v>
+      </x:c>
+      <x:c r="Q616" t="str">
+        <x:v>Defence programme</x:v>
+      </x:c>
+      <x:c r="R616" t="str">
+        <x:v>Seaspan / Babcock Canada</x:v>
+      </x:c>
+      <x:c r="S616" t="str">
+        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
+      </x:c>
+      <x:c r="T616" t="str">
+        <x:v>Extension through 2032</x:v>
+      </x:c>
+      <x:c r="U616" t="str"/>
+      <x:c r="V616" t="str"/>
+      <x:c r="W616" t="str">
+        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
+      </x:c>
+      <x:c r="X616" t="str">
+        <x:v>Canadian submarine MRO continuity</x:v>
+      </x:c>
+      <x:c r="Y616" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="Z616" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA616" t="str">
+        <x:v>SRC134_004</x:v>
+      </x:c>
+      <x:c r="AB616" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC616" t="str">
+        <x:v>Do not infer contract value or expanded scope beyond the source headline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617">
+      <x:c r="A617" t="str">
+        <x:v>OBS_000616</x:v>
+      </x:c>
+      <x:c r="B617" t="str">
+        <x:v>EVT134_003</x:v>
+      </x:c>
+      <x:c r="C617" t="str">
+        <x:v>news_intake_v1_34</x:v>
+      </x:c>
+      <x:c r="D617" t="str">
+        <x:v>NEWS134_003</x:v>
+      </x:c>
+      <x:c r="E617" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F617" t="str">
+        <x:v>Regulatory / Enforcement</x:v>
+      </x:c>
+      <x:c r="G617" t="str">
+        <x:v>Enforcement</x:v>
+      </x:c>
+      <x:c r="H617" t="str">
+        <x:v>MARPOL / APPS oily-waste discharge</x:v>
+      </x:c>
+      <x:c r="I617" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J617" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="K617" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="L617" t="str">
+        <x:v>Port of Philadelphia / Delaware River</x:v>
+      </x:c>
+      <x:c r="M617" t="str"/>
+      <x:c r="N617" t="str"/>
+      <x:c r="O617" t="str">
+        <x:v>MSC SAMIRA III</x:v>
+      </x:c>
+      <x:c r="P617" t="str">
+        <x:v>VES_MSC_SAMIRA_III</x:v>
+      </x:c>
+      <x:c r="Q617" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="R617" t="str">
+        <x:v>MSC Shipmanagement / Hong Kong Spirit</x:v>
+      </x:c>
+      <x:c r="S617" t="str">
+        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
+      </x:c>
+      <x:c r="T617" t="str">
+        <x:v>USD 1.75m combined fine; four years' probation each</x:v>
+      </x:c>
+      <x:c r="U617" t="str"/>
+      <x:c r="V617" t="str"/>
+      <x:c r="W617" t="str">
+        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
+      </x:c>
+      <x:c r="X617" t="str">
+        <x:v>Environmental-compliance and reputational exposure</x:v>
+      </x:c>
+      <x:c r="Y617" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="Z617" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA617" t="str">
+        <x:v>SRC134_005</x:v>
+      </x:c>
+      <x:c r="AB617" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC617" t="str">
+        <x:v>Vessel identifiers beyond name require registry verification.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618">
+      <x:c r="A618" t="str">
+        <x:v>OBS_000617</x:v>
+      </x:c>
+      <x:c r="B618" t="str">
+        <x:v>EVT134_004</x:v>
+      </x:c>
+      <x:c r="C618" t="str">
+        <x:v>news_intake_v1_34</x:v>
+      </x:c>
+      <x:c r="D618" t="str">
+        <x:v>NEWS134_004</x:v>
+      </x:c>
+      <x:c r="E618" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F618" t="str">
+        <x:v>Workforce / Industrial Capacity</x:v>
+      </x:c>
+      <x:c r="G618" t="str">
+        <x:v>Programme expansion</x:v>
+      </x:c>
+      <x:c r="H618" t="str">
+        <x:v>Training-center designations</x:v>
+      </x:c>
+      <x:c r="I618" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J618" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="K618" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="L618" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="M618" t="str"/>
+      <x:c r="N618" t="str"/>
+      <x:c r="O618" t="str">
+        <x:v>Maritime workforce training network</x:v>
+      </x:c>
+      <x:c r="P618" t="str">
+        <x:v>ORG_MARAD</x:v>
+      </x:c>
+      <x:c r="Q618" t="str">
+        <x:v>Training programme</x:v>
+      </x:c>
+      <x:c r="R618" t="str">
+        <x:v>MARAD</x:v>
+      </x:c>
+      <x:c r="S618" t="str">
+        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="T618" t="str">
+        <x:v>16 additional institutions designated</x:v>
+      </x:c>
+      <x:c r="U618" t="str"/>
+      <x:c r="V618" t="str"/>
+      <x:c r="W618" t="str">
+        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
+      </x:c>
+      <x:c r="X618" t="str">
+        <x:v>Workforce capacity for shipbuilding and mariner supply</x:v>
+      </x:c>
+      <x:c r="Y618" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="Z618" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA618" t="str">
+        <x:v>SRC134_006</x:v>
+      </x:c>
+      <x:c r="AB618" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC618" t="str">
+        <x:v>Five institutions named in source captured; full 16-institution roster remains a research item.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619">
+      <x:c r="A619" t="str">
+        <x:v>OBS_000618</x:v>
+      </x:c>
+      <x:c r="B619" t="str">
+        <x:v>EVT134_005</x:v>
+      </x:c>
+      <x:c r="C619" t="str">
+        <x:v>news_intake_v1_34</x:v>
+      </x:c>
+      <x:c r="D619" t="str">
+        <x:v>NEWS134_005</x:v>
+      </x:c>
+      <x:c r="E619" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="F619" t="str">
+        <x:v>Commercial / Legal</x:v>
+      </x:c>
+      <x:c r="G619" t="str">
+        <x:v>Commercial / legal dispute</x:v>
+      </x:c>
+      <x:c r="H619" t="str">
+        <x:v>Shipbuilding arbitration</x:v>
+      </x:c>
+      <x:c r="I619" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="J619" t="str">
+        <x:v>Russian Arctic / South Korea</x:v>
+      </x:c>
+      <x:c r="K619" t="str">
+        <x:v>Russia / South Korea</x:v>
+      </x:c>
+      <x:c r="L619" t="str">
+        <x:v>Singapore arbitration / Geoje shipbuilding</x:v>
+      </x:c>
+      <x:c r="M619" t="str"/>
+      <x:c r="N619" t="str"/>
+      <x:c r="O619" t="str">
+        <x:v>Arctic LNG 2 Arc7 carrier programme</x:v>
+      </x:c>
+      <x:c r="P619" t="str">
+        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
+      </x:c>
+      <x:c r="Q619" t="str">
+        <x:v>Shipbuilding programme</x:v>
+      </x:c>
+      <x:c r="R619" t="str">
+        <x:v>Arctic LNG 2 / Hanwha Ocean</x:v>
+      </x:c>
+      <x:c r="S619" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
+      </x:c>
+      <x:c r="T619" t="str">
+        <x:v>USD 1.02bn claim filed at SIAC</x:v>
+      </x:c>
+      <x:c r="U619" t="str"/>
+      <x:c r="V619" t="str"/>
+      <x:c r="W619" t="str">
+        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
+      </x:c>
+      <x:c r="X619" t="str">
+        <x:v>Arctic LNG export-fleet and sanctions risk</x:v>
+      </x:c>
+      <x:c r="Y619" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="Z619" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="AA619" t="str">
+        <x:v>SRC134_008</x:v>
+      </x:c>
+      <x:c r="AB619" t="str">
+        <x:v>Canonical event resolved</x:v>
+      </x:c>
+      <x:c r="AC619" t="str">
+        <x:v>Sanctions and canceled carrier orders are central context.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R30db454c71b846b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R72528468526a4c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R273618b80968497b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R00e84d71528946a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R67025ecbb94c429d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R6b70132e45fa4974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Rdbdade14ce8f48cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rc2b67467b50a40fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rf2fb2202758149ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R394cf27e44024963"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R76d87421dee34625"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R957d0b8292974658"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rae86b3fe47494ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Ree4d1af6feab4730"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6d33db539f144fd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R9228566fc3e14a01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R63c3f7d10a2a430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Ra33620a56046462d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rff57b260c78b4e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rac7923df43f14731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R9f7c089e8ddf41f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R2d14de369b7b4d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R322409c57b034096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="Rb42f82794dad48a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R4ca3cbc05227430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Ra47f726ca10c47ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R746195267748470b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Rd58622a8fba847ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5040,224 +5040,220 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>NEWSV1251_01</x:v>
+        <x:v>NEWS00021</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>2026-08-24</x:v>
+        <x:v>2026-09-10</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Davie awarded C$11.3bn contract to build six Canadian Coast Guard Program Icebreakers</x:v>
+        <x:v>Gulftainer enters Thailand with Suksawat terminal investment</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>Davie</x:v>
+        <x:v>Splash247</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
+        <x:v>https://splash247.com/gulftainer-enters-thailand-with-suksawat-terminal-investment/</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>Davie, part of Inocea, secured a fixed-price C$11.3bn contract for six Program Icebreakers.</x:v>
+        <x:v>Gulftainer signed a binding agreement to invest in Suksawat Terminal, establishing its first operating foothold in Thailand.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>North America</x:v>
+        <x:v>Southeast Asia</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
-        <x:v>Canada</x:v>
+        <x:v>Thailand</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Shipbuilding / Arctic / Defence</x:v>
+        <x:v>Ports / Logistics / Investment</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Contract award</x:v>
+        <x:v>Corporate investment</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
-        <x:v>Icebreaker programme</x:v>
-      </x:c>
-      <x:c r="L22" s="14" t="str"/>
+        <x:v>Terminal investment / market entry</x:v>
+      </x:c>
+      <x:c r="L22" s="14"/>
       <x:c r="M22" s="14" t="str">
-        <x:v>Official / primary</x:v>
+        <x:v>Reported; primary release corroborates</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>SRC_V1251_002</x:v>
+        <x:v>SRC_0381</x:v>
       </x:c>
       <x:c r="O22" s="14" t="str">
-        <x:v>Links Inocea, Davie and Arctic trade-support capacity.</x:v>
+        <x:v>Stake and financial terms not disclosed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>NEWSV1251_02</x:v>
+        <x:v>NEWS00022</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>2025-12-02</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Davie Defense closes acquisition of Gulf Copper shipbuilding assets in Texas</x:v>
+        <x:v>Gulftainer Expands into Thailand with Strategic Investment in Suksawat Terminal</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Davie</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>https://www.davie.ca/en/news/davie-defense-closes-gulf-copper-acquisition-confirming-u-s-shipbuilding-expansion/</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-expands-to-thailand-terminal/</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>Davie Defense completed its acquisition of Gulf Copper shipbuilding assets in Galveston and Port Arthur.</x:v>
+        <x:v>Strategic investment will support terminal capacity, productivity and services and serve as a platform for wider Thailand expansion.</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>North America</x:v>
+        <x:v>Southeast Asia</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str">
-        <x:v>United States</x:v>
+        <x:v>Thailand</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Shipbuilding / M&amp;A</x:v>
+        <x:v>Ports / Logistics / Investment</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Transaction</x:v>
+        <x:v>Corporate investment</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
-        <x:v>Acquisition completed</x:v>
-      </x:c>
-      <x:c r="L23" s="14" t="str"/>
+        <x:v>Terminal investment / market entry</x:v>
+      </x:c>
+      <x:c r="L23" s="14"/>
       <x:c r="M23" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>SRC_V1251_004</x:v>
-      </x:c>
-      <x:c r="O23" s="14" t="str">
-        <x:v>Expands Inocea's U.S. industrial footprint.</x:v>
-      </x:c>
+        <x:v>SRC_0380</x:v>
+      </x:c>
+      <x:c r="O23" s="14"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>NEWSV1251_03</x:v>
+        <x:v>NEWS00023</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Seaspan and Maersk advance fleet-efficiency upgrade programme across 18 chartered vessels</x:v>
+        <x:v>Gulftainer unveils global trade infrastructure strategy</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>Seaspan Corporation</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>https://www.seaspancorp.com/news/seaspan-and-maersk-advance-fleet-efficiency-through-strategic-vessel-upgrade-program/</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Seaspan and Maersk are advancing efficiency upgrades across 18 long-term chartered vessels.</x:v>
+        <x:v>Strategy targets 10+ million TEU future port capacity, 2.3 million TEU inland logistics capacity and integrated trade corridors.</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="H24" s="14" t="str"/>
+        <x:v>Middle East / Global</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str">
+        <x:v>United Arab Emirates</x:v>
+      </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Shipping / Fleet / Decarbonisation</x:v>
+        <x:v>Ports / Logistics / Strategy</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Fleet programme</x:v>
+        <x:v>Corporate strategy</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>Retrofit / charter partnership</x:v>
-      </x:c>
-      <x:c r="L24" s="14" t="str"/>
+        <x:v>Integrated trade infrastructure</x:v>
+      </x:c>
+      <x:c r="L24" s="14"/>
       <x:c r="M24" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>SRC_V1251_007</x:v>
-      </x:c>
-      <x:c r="O24" s="14" t="str">
-        <x:v>Links shipowner, charterer and vessel fleet.</x:v>
-      </x:c>
+        <x:v>SRC_0040</x:v>
+      </x:c>
+      <x:c r="O24" s="14"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>NEWSV1251_04</x:v>
+        <x:v>NEWS00024</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>2026-08-27</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Seaspan receives investment-grade issuer rating upgrade from KBRA</x:v>
+        <x:v>Gulftainer strengthens Iraq gateway with dedicated GT Lines service</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Seaspan Corporation</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>https://www.seaspancorp.com/news/seaspan-achieves-investment-grade-rating-upgrade-from-kbra/</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer-strengthens-iraq-trade-gateway/</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>KBRA upgraded Seaspan's issuer and senior unsecured ratings to BBB-.</x:v>
+        <x:v>Dedicated feeder service connects UAE and Umm Qasr through Gulftainer-controlled terminal, logistics and vessel layers.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Global</x:v>
-      </x:c>
-      <x:c r="H25" s="14" t="str"/>
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str">
+        <x:v>Iraq / UAE</x:v>
+      </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>Shipping / Finance</x:v>
+        <x:v>Shipping / Ports / Logistics</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Corporate / credit</x:v>
+        <x:v>Service expansion</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>Rating upgrade</x:v>
-      </x:c>
-      <x:c r="L25" s="14" t="str"/>
+        <x:v>Integrated feeder corridor</x:v>
+      </x:c>
+      <x:c r="L25" s="14"/>
       <x:c r="M25" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>SRC_V1251_009</x:v>
-      </x:c>
-      <x:c r="O25" s="14" t="str">
-        <x:v>Corporate finance signal tied to fleet scale and charter book.</x:v>
-      </x:c>
+        <x:v>SRC_0382</x:v>
+      </x:c>
+      <x:c r="O25" s="14"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>NEWSV1251_05</x:v>
+        <x:v>NEWS00025</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>AD Ports Group agrees AED 3.1bn acquisition of Brazilian agri-bulk terminal operator CLI</x:v>
+        <x:v>Gulftainer unveils Al Dhaid Multi-Modal Trade Corridor</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>AD Ports Group</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/06/02/ad-ports-group-acquires-cli</x:v>
+        <x:v>https://www.gulftainer.com/news/releases/gulftainer_unveils_aldhaid_trade_corridor/</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>AD Ports agreed to acquire CLI from Macquarie Asset Management and IG4 Capital; CLI operates terminals at Santos and Itaqui.</x:v>
+        <x:v>150-hectare inland logistics development is designed as a 1.5 million TEU annual-capacity extension to Khorfakkan.</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>Latin America / Middle East</x:v>
+        <x:v>Middle East</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str">
-        <x:v>Brazil / UAE</x:v>
+        <x:v>United Arab Emirates</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
-        <x:v>Ports / Infrastructure / M&amp;A</x:v>
+        <x:v>Logistics / Infrastructure</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Transaction</x:v>
+        <x:v>Infrastructure investment</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>Acquisition pending</x:v>
-      </x:c>
-      <x:c r="L26" s="14" t="str"/>
+        <x:v>Multimodal inland corridor</x:v>
+      </x:c>
+      <x:c r="L26" s="14"/>
       <x:c r="M26" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>SRC_V1251_005</x:v>
-      </x:c>
-      <x:c r="O26" s="14" t="str">
-        <x:v>Links buyer, sellers, CLI and both terminal gateways.</x:v>
-      </x:c>
+        <x:v>SRC_0041</x:v>
+      </x:c>
+      <x:c r="O26" s="14"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
@@ -7493,19 +7489,19 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="14" t="str">
-        <x:v>NLINKV12507</x:v>
+        <x:v>NLINK00048</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
-        <x:v>NEWSV12503</x:v>
+        <x:v>NEWS00021</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>COMP_QUBE</x:v>
+        <x:v>COMP_GULFTAINER</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
-        <x:v>TARGET</x:v>
+        <x:v>INVESTOR</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7513,23 +7509,25 @@
       <x:c r="G48" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="H48" s="14"/>
+      <x:c r="H48" s="14" t="str">
+        <x:v>Gulftainer</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="14" t="str">
-        <x:v>NLINKV1251_001</x:v>
+        <x:v>NLINK00049</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
-        <x:v>NEWSV1251_01</x:v>
+        <x:v>NEWS00021</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>COMP_DAVIE</x:v>
+        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
-        <x:v>SUBJECT</x:v>
+        <x:v>TARGET / OPERATING PLATFORM</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7538,24 +7536,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
-        <x:v>Davie contract award</x:v>
+        <x:v>Suksawat Terminal Co.</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="14" t="str">
-        <x:v>NLINKV1251_002</x:v>
+        <x:v>NLINK00050</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>NEWSV1251_01</x:v>
+        <x:v>NEWS00021</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>COMP_INOCEA</x:v>
+        <x:v>TERM0530</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>Company</x:v>
+        <x:v>Terminal</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>PARENT</x:v>
+        <x:v>TARGET ASSET</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7564,24 +7562,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>Inocea parent group</x:v>
+        <x:v>Suksawat Terminal</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="14" t="str">
-        <x:v>NLINKV1251_003</x:v>
+        <x:v>NLINK00051</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
-        <x:v>NEWSV1251_02</x:v>
+        <x:v>NEWS00022</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>COMP_DAVIE_DEFENSE</x:v>
+        <x:v>COMP_GULFTAINER</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>BUYER</x:v>
+        <x:v>INVESTOR</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7590,24 +7588,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>U.S. acquisition vehicle</x:v>
+        <x:v>Gulftainer</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
-        <x:v>NLINKV1251_004</x:v>
+        <x:v>NLINK00052</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>NEWSV1251_02</x:v>
+        <x:v>NEWS00022</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>COMP_GULF_COPPER</x:v>
+        <x:v>TERM0530</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>Company</x:v>
+        <x:v>Terminal</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>TARGET / ASSET</x:v>
+        <x:v>TARGET ASSET</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7616,44 +7614,44 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
-        <x:v>Texas shipyard group</x:v>
+        <x:v>Suksawat Terminal</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
-        <x:v>NLINKV1251_005</x:v>
+        <x:v>NLINK00053</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>NEWSV1251_02</x:v>
+        <x:v>NEWS00023</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>COMP_INOCEA</x:v>
+        <x:v>COMP_GULFTAINER</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>PARENT</x:v>
+        <x:v>SUBJECT</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>Secondary</x:v>
+        <x:v>Primary</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>Parent group</x:v>
+        <x:v>Global strategy</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="14" t="str">
-        <x:v>NLINKV1251_006</x:v>
+        <x:v>NLINK00054</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
-        <x:v>NEWSV1251_03</x:v>
+        <x:v>NEWS00024</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>COMP_SEASPAN_CORP</x:v>
+        <x:v>COMP_GULFTAINER</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
         <x:v>Company</x:v>
@@ -7668,24 +7666,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str">
-        <x:v>Fleet owner</x:v>
+        <x:v>GT Lines / Iraq corridor</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="14" t="str">
-        <x:v>NLINKV1251_007</x:v>
+        <x:v>NLINK00055</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
-        <x:v>NEWSV1251_03</x:v>
+        <x:v>NEWS00025</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>COMP_MAERSK</x:v>
+        <x:v>COMP_GULFTAINER</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>CHARTER PARTNER</x:v>
+        <x:v>SUBJECT</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7694,7 +7692,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str">
-        <x:v>Charterer</x:v>
+        <x:v>Al Dhaid corridor</x:v>
       </x:c>
     </x:row>
     <x:row r="56">

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R6d33db539f144fd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R9228566fc3e14a01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R63c3f7d10a2a430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Ra33620a56046462d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rff57b260c78b4e87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rac7923df43f14731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R9f7c089e8ddf41f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R2d14de369b7b4d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R322409c57b034096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="Rb42f82794dad48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R4ca3cbc05227430f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Ra47f726ca10c47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R746195267748470b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Rd58622a8fba847ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R27776bde0b1b4958"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R7250e41f32eb4a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Ra6ba31169a234a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rbefd781819314e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R2d6665c2e14c4ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rfb140e4914f8494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R27d2b9127ab54f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R71f9591f59b34031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rd0cf685deb814d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R5514995fc31a4707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R2f4f4408d47949b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Rd3c02416cc0642d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R240c022d7ccb407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R41fed3352bbc43e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Product View" sheetId="15" r:id="Rde70080dacc14de8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +27,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -49,8 +50,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFD8B45A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -67,6 +74,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF11161A"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -75,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -101,6 +113,11 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -900,6 +917,161 @@
         <x:v>Counts are conservative lower bounds during wartime jamming; September 2026 is partial.</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>MON_SEC_001</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>PGSA Maritime Compliance &amp; Secondary Exposure</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>Security / Compliance</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Strait of Hormuz / Gulf of Oman</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>24h to months</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>New PGSA designations, enforcement, delistings, STS counterparties and commercial avoidance</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>New vessels listed; detention/diversion; STS interaction; owner/operator changes; future Hormuz passage; delisting request</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>Confirmed enforcement against listed/counterparty vessel or material expansion of list</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="str">
+        <x:v>EVT_SEC_PGSA</x:v>
+      </x:c>
+      <x:c r="L8" s="14" t="str">
+        <x:v>VESSEL_00024;VESSEL_00075;VESSEL_SEC_001;VESSEL_SEC_002</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="str">
+        <x:v>SRC_PGSA_PC</x:v>
+      </x:c>
+      <x:c r="N8" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="O8" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="P8" s="14" t="str">
+        <x:v>Material change</x:v>
+      </x:c>
+      <x:c r="Q8" s="14" t="str">
+        <x:v>Core P&amp;C Intelligence compliance watch; feeds Trade System company/vessel exposure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>MON_SEC_002</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>East Asia Official MARSEC Incident Watch</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>Security / Maritime Safety</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Japan / South Korea</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>Daily / ongoing</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>Official coast-guard reporting on groundings, collisions, fires, rescues, pollution and navigation hazards</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>New casualty; merchant-vessel involvement; port/channel restriction; pollution; fatalities; major SAR deployment</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>Commercial vessel casualty or disruption to a tracked port/corridor</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="str">
+        <x:v>EVT_SEC_001;EVT_SEC_002</x:v>
+      </x:c>
+      <x:c r="L9" s="14"/>
+      <x:c r="M9" s="14" t="str">
+        <x:v>SRC_JCG;SRC_KCG</x:v>
+      </x:c>
+      <x:c r="N9" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="O9" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="P9" s="14" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="Q9" s="14" t="str">
+        <x:v>Official-source discovery should resolve vessel, company, port and corridor before alerting.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>MON_SEC_003</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>India MARSEC Casualty &amp; Pollution Watch</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>Security / Maritime Safety</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>India / Indian Ocean approaches</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>Daily / ongoing</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>ICG and DG Shipping casualty, SAR, pollution and safety investigation reporting</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>Grounding; fire; loss of stability; spill; port restriction; investigation circular</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>Merchant casualty with trade, port or pollution consequence</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="str">
+        <x:v>EVT_SEC_003</x:v>
+      </x:c>
+      <x:c r="L10" s="14"/>
+      <x:c r="M10" s="14" t="str">
+        <x:v>SRC_ICG;SRC_DGS_INDIA</x:v>
+      </x:c>
+      <x:c r="N10" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="O10" s="14" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="P10" s="14" t="str">
+        <x:v>Daily</x:v>
+      </x:c>
+      <x:c r="Q10" s="14" t="str">
+        <x:v>Use ICG for response/operations and DGS for casualty/regulatory follow-up.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4074,6 +4246,271 @@
       <x:c r="U26" s="14"/>
       <x:c r="V26" s="14"/>
       <x:c r="W26" s="14"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>View ID</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>Object</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>Canonical ID / Source</x:v>
+      </x:c>
+      <x:c r="E1" s="19" t="str">
+        <x:v>Display Label</x:v>
+      </x:c>
+      <x:c r="F1" s="19" t="str">
+        <x:v>Security Lens</x:v>
+      </x:c>
+      <x:c r="G1" s="19" t="str">
+        <x:v>Trade-System Lens</x:v>
+      </x:c>
+      <x:c r="H1" s="19" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="I1" s="19" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="J1" s="19" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>SPV_001</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>VESSEL_00024</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>Mraweh</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>PGSA listed vessel; STS exposure; Hormuz future-access risk</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>ADNOC L&amp;S fleet asset; LNG trade exposure</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>Same canonical vessel record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>SPV_002</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>VESSEL_SEC_001</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>GasLog Shanghai</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>PGSA listed vessel; STS counterparty propagation</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>GasLog fleet / LNG trade / ownership</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>Same canonical vessel record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>SPV_003</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>Event</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>EVT_SEC_002</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>Jawoldo grounding</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>Grounding/SAR event; official KCG source</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>Local maritime disruption / vessel operating risk</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>Same event can feed both applications.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>SPV_004</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>Source Feed</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>FEED_SEC_001</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>Japan Coast Guard</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>Primary MARSEC discovery / confirmation</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>Event enrichment for vessel/port/corridor records</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>Official source feed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>SPV_005</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Source Feed</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>FEED_SEC_003</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Korea Coast Guard</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>Primary MARSEC discovery / confirmation</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>Event enrichment for vessel/port/corridor records</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>Official source feed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>SPV_006</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>Source Feed</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>FEED_SEC_004</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>Indian Coast Guard</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>SAR/casualty/pollution operational reporting</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>Event and infrastructure exposure</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>Official source feed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>SPV_007</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>P&amp;C Intelligence</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>Source Feed</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>FEED_SEC_005</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>DG Shipping India</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>Casualty investigation / safety regulation</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>Regulatory and operating-risk enrichment</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>Official regulatory feed.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,21 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R27776bde0b1b4958"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R7250e41f32eb4a77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Ra6ba31169a234a2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rbefd781819314e76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R2d6665c2e14c4ba4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rfb140e4914f8494b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R27d2b9127ab54f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R71f9591f59b34031"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="Rd0cf685deb814d6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R5514995fc31a4707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R2f4f4408d47949b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Rd3c02416cc0642d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R240c022d7ccb407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R41fed3352bbc43e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Product View" sheetId="15" r:id="Rde70080dacc14de8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R3e294904853b4444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R68fd75bc95a843aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R8b3ff927bdb04c62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rb4f3d5fe51704d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rbcb9f151a32d4ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R8aff96186b014ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R31d5b2cbf772443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="Rcc0c3cf7c0744c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R086dc8c413a24197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R9a8ca29473b04b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R7fbe8ac5747241f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="Rc5fdfb6903b64709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rce3f8f21740e45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Re8366ceccd2d4bdf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,7 +26,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,14 +49,8 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFD8B45A"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,11 +67,6 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF11161A"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -87,7 +75,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -113,11 +101,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -864,214 +847,6 @@
         <x:v>Designed for cross-event pattern analysis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>MON134_001</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>Strait of Hormuz traffic and AIS confidence</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Security / Trade Flow</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Persian Gulf / Strait of Hormuz / Gulf of Oman</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>2026-03-08</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>Daily to monthly</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>AIS-derived crossings, direction, tanker movements and estimated oil exports</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>Crossings; inbound/outbound balance; outbound oil tankers; estimated oil; ship counts by zone; AIS coverage caveats</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>Material traffic recovery/deterioration or change in AIS coverage confidence</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>EVT134_001</x:v>
-      </x:c>
-      <x:c r="L7" t="str">
-        <x:v>SYS_HORMUZ_SECURITY</x:v>
-      </x:c>
-      <x:c r="M7" t="str">
-        <x:v>SRC134_001</x:v>
-      </x:c>
-      <x:c r="N7" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="O7" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="P7" t="str">
-        <x:v>Monthly close / 30-minute API refresh</x:v>
-      </x:c>
-      <x:c r="Q7" t="str">
-        <x:v>Counts are conservative lower bounds during wartime jamming; September 2026 is partial.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>MON_SEC_001</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>PGSA Maritime Compliance &amp; Secondary Exposure</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>Security / Compliance</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>Strait of Hormuz / Gulf of Oman</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="str">
-        <x:v>2026-08-24</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>24h to months</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="str">
-        <x:v>New PGSA designations, enforcement, delistings, STS counterparties and commercial avoidance</x:v>
-      </x:c>
-      <x:c r="I8" s="14" t="str">
-        <x:v>New vessels listed; detention/diversion; STS interaction; owner/operator changes; future Hormuz passage; delisting request</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="str">
-        <x:v>Confirmed enforcement against listed/counterparty vessel or material expansion of list</x:v>
-      </x:c>
-      <x:c r="K8" s="14" t="str">
-        <x:v>EVT_SEC_PGSA</x:v>
-      </x:c>
-      <x:c r="L8" s="14" t="str">
-        <x:v>VESSEL_00024;VESSEL_00075;VESSEL_SEC_001;VESSEL_SEC_002</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="str">
-        <x:v>SRC_PGSA_PC</x:v>
-      </x:c>
-      <x:c r="N8" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="O8" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="P8" s="14" t="str">
-        <x:v>Material change</x:v>
-      </x:c>
-      <x:c r="Q8" s="14" t="str">
-        <x:v>Core P&amp;C Intelligence compliance watch; feeds Trade System company/vessel exposure.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>MON_SEC_002</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>East Asia Official MARSEC Incident Watch</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="str">
-        <x:v>Security / Maritime Safety</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="str">
-        <x:v>Japan / South Korea</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="str">
-        <x:v>Daily / ongoing</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="str">
-        <x:v>Official coast-guard reporting on groundings, collisions, fires, rescues, pollution and navigation hazards</x:v>
-      </x:c>
-      <x:c r="I9" s="14" t="str">
-        <x:v>New casualty; merchant-vessel involvement; port/channel restriction; pollution; fatalities; major SAR deployment</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="str">
-        <x:v>Commercial vessel casualty or disruption to a tracked port/corridor</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="str">
-        <x:v>EVT_SEC_001;EVT_SEC_002</x:v>
-      </x:c>
-      <x:c r="L9" s="14"/>
-      <x:c r="M9" s="14" t="str">
-        <x:v>SRC_JCG;SRC_KCG</x:v>
-      </x:c>
-      <x:c r="N9" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="O9" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="P9" s="14" t="str">
-        <x:v>Daily</x:v>
-      </x:c>
-      <x:c r="Q9" s="14" t="str">
-        <x:v>Official-source discovery should resolve vessel, company, port and corridor before alerting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>MON_SEC_003</x:v>
-      </x:c>
-      <x:c r="B10" s="14" t="str">
-        <x:v>India MARSEC Casualty &amp; Pollution Watch</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="str">
-        <x:v>Security / Maritime Safety</x:v>
-      </x:c>
-      <x:c r="D10" s="14" t="str">
-        <x:v>India / Indian Ocean approaches</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="str">
-        <x:v>Daily / ongoing</x:v>
-      </x:c>
-      <x:c r="H10" s="14" t="str">
-        <x:v>ICG and DG Shipping casualty, SAR, pollution and safety investigation reporting</x:v>
-      </x:c>
-      <x:c r="I10" s="14" t="str">
-        <x:v>Grounding; fire; loss of stability; spill; port restriction; investigation circular</x:v>
-      </x:c>
-      <x:c r="J10" s="14" t="str">
-        <x:v>Merchant casualty with trade, port or pollution consequence</x:v>
-      </x:c>
-      <x:c r="K10" s="14" t="str">
-        <x:v>EVT_SEC_003</x:v>
-      </x:c>
-      <x:c r="L10" s="14"/>
-      <x:c r="M10" s="14" t="str">
-        <x:v>SRC_ICG;SRC_DGS_INDIA</x:v>
-      </x:c>
-      <x:c r="N10" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="O10" s="14" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="P10" s="14" t="str">
-        <x:v>Daily</x:v>
-      </x:c>
-      <x:c r="Q10" s="14" t="str">
-        <x:v>Use ICG for response/operations and DGS for casualty/regulatory follow-up.</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4252,271 +4027,6 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="19" t="str">
-        <x:v>View ID</x:v>
-      </x:c>
-      <x:c r="B1" s="19" t="str">
-        <x:v>Product</x:v>
-      </x:c>
-      <x:c r="C1" s="19" t="str">
-        <x:v>Object</x:v>
-      </x:c>
-      <x:c r="D1" s="19" t="str">
-        <x:v>Canonical ID / Source</x:v>
-      </x:c>
-      <x:c r="E1" s="19" t="str">
-        <x:v>Display Label</x:v>
-      </x:c>
-      <x:c r="F1" s="19" t="str">
-        <x:v>Security Lens</x:v>
-      </x:c>
-      <x:c r="G1" s="19" t="str">
-        <x:v>Trade-System Lens</x:v>
-      </x:c>
-      <x:c r="H1" s="19" t="str">
-        <x:v>Priority</x:v>
-      </x:c>
-      <x:c r="I1" s="19" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="J1" s="19" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>SPV_001</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="D2" s="14" t="str">
-        <x:v>VESSEL_00024</x:v>
-      </x:c>
-      <x:c r="E2" s="14" t="str">
-        <x:v>Mraweh</x:v>
-      </x:c>
-      <x:c r="F2" s="14" t="str">
-        <x:v>PGSA listed vessel; STS exposure; Hormuz future-access risk</x:v>
-      </x:c>
-      <x:c r="G2" s="14" t="str">
-        <x:v>ADNOC L&amp;S fleet asset; LNG trade exposure</x:v>
-      </x:c>
-      <x:c r="H2" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="I2" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J2" s="14" t="str">
-        <x:v>Same canonical vessel record.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>SPV_002</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>VESSEL_SEC_001</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>GasLog Shanghai</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="str">
-        <x:v>PGSA listed vessel; STS counterparty propagation</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>GasLog fleet / LNG trade / ownership</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J3" s="14" t="str">
-        <x:v>Same canonical vessel record.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="14" t="str">
-        <x:v>SPV_003</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C4" s="14" t="str">
-        <x:v>Event</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str">
-        <x:v>EVT_SEC_002</x:v>
-      </x:c>
-      <x:c r="E4" s="14" t="str">
-        <x:v>Jawoldo grounding</x:v>
-      </x:c>
-      <x:c r="F4" s="14" t="str">
-        <x:v>Grounding/SAR event; official KCG source</x:v>
-      </x:c>
-      <x:c r="G4" s="14" t="str">
-        <x:v>Local maritime disruption / vessel operating risk</x:v>
-      </x:c>
-      <x:c r="H4" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="I4" s="14" t="str">
-        <x:v>Closed</x:v>
-      </x:c>
-      <x:c r="J4" s="14" t="str">
-        <x:v>Same event can feed both applications.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>SPV_004</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C5" s="14" t="str">
-        <x:v>Source Feed</x:v>
-      </x:c>
-      <x:c r="D5" s="14" t="str">
-        <x:v>FEED_SEC_001</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>Japan Coast Guard</x:v>
-      </x:c>
-      <x:c r="F5" s="14" t="str">
-        <x:v>Primary MARSEC discovery / confirmation</x:v>
-      </x:c>
-      <x:c r="G5" s="14" t="str">
-        <x:v>Event enrichment for vessel/port/corridor records</x:v>
-      </x:c>
-      <x:c r="H5" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="I5" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J5" s="14" t="str">
-        <x:v>Official source feed.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>SPV_005</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>Source Feed</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>FEED_SEC_003</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Korea Coast Guard</x:v>
-      </x:c>
-      <x:c r="F6" s="14" t="str">
-        <x:v>Primary MARSEC discovery / confirmation</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>Event enrichment for vessel/port/corridor records</x:v>
-      </x:c>
-      <x:c r="H6" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="I6" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J6" s="14" t="str">
-        <x:v>Official source feed.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>SPV_006</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>Source Feed</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>FEED_SEC_004</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>Indian Coast Guard</x:v>
-      </x:c>
-      <x:c r="F7" s="14" t="str">
-        <x:v>SAR/casualty/pollution operational reporting</x:v>
-      </x:c>
-      <x:c r="G7" s="14" t="str">
-        <x:v>Event and infrastructure exposure</x:v>
-      </x:c>
-      <x:c r="H7" s="14" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="I7" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J7" s="14" t="str">
-        <x:v>Official source feed.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>SPV_007</x:v>
-      </x:c>
-      <x:c r="B8" s="14" t="str">
-        <x:v>P&amp;C Intelligence</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="str">
-        <x:v>Source Feed</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
-        <x:v>FEED_SEC_005</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="str">
-        <x:v>DG Shipping India</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="str">
-        <x:v>Casualty investigation / safety regulation</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>Regulatory and operating-risk enrichment</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="I8" s="14" t="str">
-        <x:v>Active</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="str">
-        <x:v>Official regulatory feed.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -5477,220 +4987,224 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>NEWS00021</x:v>
+        <x:v>NEWSV1251_01</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>2026-09-10</x:v>
+        <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Gulftainer enters Thailand with Suksawat terminal investment</x:v>
+        <x:v>Davie awarded C$11.3bn contract to build six Canadian Coast Guard Program Icebreakers</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>Splash247</x:v>
+        <x:v>Davie</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>https://splash247.com/gulftainer-enters-thailand-with-suksawat-terminal-investment/</x:v>
+        <x:v>https://www.davie.ca/en/news/20260824-pib-anoouncement-en/</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>Gulftainer signed a binding agreement to invest in Suksawat Terminal, establishing its first operating foothold in Thailand.</x:v>
+        <x:v>Davie, part of Inocea, secured a fixed-price C$11.3bn contract for six Program Icebreakers.</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>Southeast Asia</x:v>
+        <x:v>North America</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
-        <x:v>Thailand</x:v>
+        <x:v>Canada</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Ports / Logistics / Investment</x:v>
+        <x:v>Shipbuilding / Arctic / Defence</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Corporate investment</x:v>
+        <x:v>Contract award</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
-        <x:v>Terminal investment / market entry</x:v>
-      </x:c>
-      <x:c r="L22" s="14"/>
+        <x:v>Icebreaker programme</x:v>
+      </x:c>
+      <x:c r="L22" s="14" t="str"/>
       <x:c r="M22" s="14" t="str">
-        <x:v>Reported; primary release corroborates</x:v>
+        <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>SRC_0381</x:v>
+        <x:v>SRC_V1251_002</x:v>
       </x:c>
       <x:c r="O22" s="14" t="str">
-        <x:v>Stake and financial terms not disclosed.</x:v>
+        <x:v>Links Inocea, Davie and Arctic trade-support capacity.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>NEWS00022</x:v>
+        <x:v>NEWSV1251_02</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>2026-09-09</x:v>
+        <x:v>2025-12-02</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Gulftainer Expands into Thailand with Strategic Investment in Suksawat Terminal</x:v>
+        <x:v>Davie Defense closes acquisition of Gulf Copper shipbuilding assets in Texas</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>Davie</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-expands-to-thailand-terminal/</x:v>
+        <x:v>https://www.davie.ca/en/news/davie-defense-closes-gulf-copper-acquisition-confirming-u-s-shipbuilding-expansion/</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>Strategic investment will support terminal capacity, productivity and services and serve as a platform for wider Thailand expansion.</x:v>
+        <x:v>Davie Defense completed its acquisition of Gulf Copper shipbuilding assets in Galveston and Port Arthur.</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>Southeast Asia</x:v>
+        <x:v>North America</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str">
-        <x:v>Thailand</x:v>
+        <x:v>United States</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Ports / Logistics / Investment</x:v>
+        <x:v>Shipbuilding / M&amp;A</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Corporate investment</x:v>
+        <x:v>Transaction</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
-        <x:v>Terminal investment / market entry</x:v>
-      </x:c>
-      <x:c r="L23" s="14"/>
+        <x:v>Acquisition completed</x:v>
+      </x:c>
+      <x:c r="L23" s="14" t="str"/>
       <x:c r="M23" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>SRC_0380</x:v>
-      </x:c>
-      <x:c r="O23" s="14"/>
+        <x:v>SRC_V1251_004</x:v>
+      </x:c>
+      <x:c r="O23" s="14" t="str">
+        <x:v>Expands Inocea's U.S. industrial footprint.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>NEWS00023</x:v>
+        <x:v>NEWSV1251_03</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Gulftainer unveils global trade infrastructure strategy</x:v>
+        <x:v>Seaspan and Maersk advance fleet-efficiency upgrade programme across 18 chartered vessels</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>Seaspan Corporation</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-unveils-global-trade-infrastructure-strategy-to-build-one-of-the-middle-easts-largest-integrated-logistics-ecosystems/</x:v>
+        <x:v>https://www.seaspancorp.com/news/seaspan-and-maersk-advance-fleet-efficiency-through-strategic-vessel-upgrade-program/</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>Strategy targets 10+ million TEU future port capacity, 2.3 million TEU inland logistics capacity and integrated trade corridors.</x:v>
+        <x:v>Seaspan and Maersk are advancing efficiency upgrades across 18 long-term chartered vessels.</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>Middle East / Global</x:v>
-      </x:c>
-      <x:c r="H24" s="14" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str"/>
       <x:c r="I24" s="14" t="str">
-        <x:v>Ports / Logistics / Strategy</x:v>
+        <x:v>Shipping / Fleet / Decarbonisation</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Corporate strategy</x:v>
+        <x:v>Fleet programme</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>Integrated trade infrastructure</x:v>
-      </x:c>
-      <x:c r="L24" s="14"/>
+        <x:v>Retrofit / charter partnership</x:v>
+      </x:c>
+      <x:c r="L24" s="14" t="str"/>
       <x:c r="M24" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>SRC_0040</x:v>
-      </x:c>
-      <x:c r="O24" s="14"/>
+        <x:v>SRC_V1251_007</x:v>
+      </x:c>
+      <x:c r="O24" s="14" t="str">
+        <x:v>Links shipowner, charterer and vessel fleet.</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>NEWS00024</x:v>
+        <x:v>NEWSV1251_04</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-08-27</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Gulftainer strengthens Iraq gateway with dedicated GT Lines service</x:v>
+        <x:v>Seaspan receives investment-grade issuer rating upgrade from KBRA</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>Seaspan Corporation</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer-strengthens-iraq-trade-gateway/</x:v>
+        <x:v>https://www.seaspancorp.com/news/seaspan-achieves-investment-grade-rating-upgrade-from-kbra/</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Dedicated feeder service connects UAE and Umm Qasr through Gulftainer-controlled terminal, logistics and vessel layers.</x:v>
+        <x:v>KBRA upgraded Seaspan's issuer and senior unsecured ratings to BBB-.</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="H25" s="14" t="str">
-        <x:v>Iraq / UAE</x:v>
-      </x:c>
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str"/>
       <x:c r="I25" s="14" t="str">
-        <x:v>Shipping / Ports / Logistics</x:v>
+        <x:v>Shipping / Finance</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Service expansion</x:v>
+        <x:v>Corporate / credit</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>Integrated feeder corridor</x:v>
-      </x:c>
-      <x:c r="L25" s="14"/>
+        <x:v>Rating upgrade</x:v>
+      </x:c>
+      <x:c r="L25" s="14" t="str"/>
       <x:c r="M25" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>SRC_0382</x:v>
-      </x:c>
-      <x:c r="O25" s="14"/>
+        <x:v>SRC_V1251_009</x:v>
+      </x:c>
+      <x:c r="O25" s="14" t="str">
+        <x:v>Corporate finance signal tied to fleet scale and charter book.</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>NEWS00025</x:v>
+        <x:v>NEWSV1251_05</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>Gulftainer unveils Al Dhaid Multi-Modal Trade Corridor</x:v>
+        <x:v>AD Ports Group agrees AED 3.1bn acquisition of Brazilian agri-bulk terminal operator CLI</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>AD Ports Group</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>https://www.gulftainer.com/news/releases/gulftainer_unveils_aldhaid_trade_corridor/</x:v>
+        <x:v>https://www.adportsgroup.com/en/news-and-media/2026/06/02/ad-ports-group-acquires-cli</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>150-hectare inland logistics development is designed as a 1.5 million TEU annual-capacity extension to Khorfakkan.</x:v>
+        <x:v>AD Ports agreed to acquire CLI from Macquarie Asset Management and IG4 Capital; CLI operates terminals at Santos and Itaqui.</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>Middle East</x:v>
+        <x:v>Latin America / Middle East</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str">
-        <x:v>United Arab Emirates</x:v>
+        <x:v>Brazil / UAE</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
-        <x:v>Logistics / Infrastructure</x:v>
+        <x:v>Ports / Infrastructure / M&amp;A</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Infrastructure investment</x:v>
+        <x:v>Transaction</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>Multimodal inland corridor</x:v>
-      </x:c>
-      <x:c r="L26" s="14"/>
+        <x:v>Acquisition pending</x:v>
+      </x:c>
+      <x:c r="L26" s="14" t="str"/>
       <x:c r="M26" s="14" t="str">
         <x:v>Official / primary</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>SRC_0041</x:v>
-      </x:c>
-      <x:c r="O26" s="14"/>
+        <x:v>SRC_V1251_005</x:v>
+      </x:c>
+      <x:c r="O26" s="14" t="str">
+        <x:v>Links buyer, sellers, CLI and both terminal gateways.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
@@ -6375,376 +5889,6 @@
       </x:c>
       <x:c r="O41" t="str">
         <x:v>Regional umbrella event for linked commercial-shipping incidents.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="str">
-        <x:v>NEWS133_001</x:v>
-      </x:c>
-      <x:c r="B42" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="C42" t="str">
-        <x:v>Peninsula confirms tanker involved in incident off Dubai</x:v>
-      </x:c>
-      <x:c r="D42" t="str">
-        <x:v>Ship &amp; Bunker</x:v>
-      </x:c>
-      <x:c r="E42" t="str">
-        <x:v>https://shipandbunker.com/news/world/583774-peninsula-confirms-tanker-involved-in-incident-off-dubai</x:v>
-      </x:c>
-      <x:c r="F42" t="str">
-        <x:v>One crewmember died and another was missing after an incident involving HERCULES STAR at anchorage off Dubai; all other crew were accounted for.</x:v>
-      </x:c>
-      <x:c r="G42" t="str">
-        <x:v>Persian Gulf</x:v>
-      </x:c>
-      <x:c r="H42" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="I42" t="str">
-        <x:v>Maritime security / bunker supply</x:v>
-      </x:c>
-      <x:c r="J42" t="str">
-        <x:v>Vessel casualty</x:v>
-      </x:c>
-      <x:c r="K42" t="str">
-        <x:v>Suspected projectile / taking water</x:v>
-      </x:c>
-      <x:c r="L42" t="str">
-        <x:v>EVT133_001</x:v>
-      </x:c>
-      <x:c r="M42" t="str">
-        <x:v>Company-confirmed casualty; attack mechanism not fully resolved</x:v>
-      </x:c>
-      <x:c r="N42" t="str">
-        <x:v>SRC133_001</x:v>
-      </x:c>
-      <x:c r="O42" t="str">
-        <x:v>Keep separate from March 2026 HERCULES STAR incident.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="str">
-        <x:v>NEWS133_002</x:v>
-      </x:c>
-      <x:c r="B43" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="C43" t="str">
-        <x:v>Nisg̱a'a, Tahltan Nations mark official opening of Stewart, B.C., port as expansion plans take shape</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
-        <x:v>CBC News</x:v>
-      </x:c>
-      <x:c r="E43" t="str">
-        <x:v>https://www.cbc.ca/news/canada/british-columbia/nisga-a-talhtan-port-opening-9.7338188</x:v>
-      </x:c>
-      <x:c r="F43" t="str">
-        <x:v>Official port opening and expansion-planning milestone involving the Nisg̱a'a and Tahltan Nations.</x:v>
-      </x:c>
-      <x:c r="G43" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="H43" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I43" t="str">
-        <x:v>Ports / infrastructure</x:v>
-      </x:c>
-      <x:c r="J43" t="str">
-        <x:v>Port opening</x:v>
-      </x:c>
-      <x:c r="K43" t="str">
-        <x:v>Expansion planning</x:v>
-      </x:c>
-      <x:c r="L43" t="str">
-        <x:v>EVT133_002</x:v>
-      </x:c>
-      <x:c r="M43" t="str">
-        <x:v>Headline verified; article detail access-limited</x:v>
-      </x:c>
-      <x:c r="N43" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-      <x:c r="O43" t="str">
-        <x:v>Do not infer ownership, operator or capacity from headline.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" t="str">
-        <x:v>NEWS133_003</x:v>
-      </x:c>
-      <x:c r="B44" t="str">
-        <x:v>2024-10-29</x:v>
-      </x:c>
-      <x:c r="C44" t="str">
-        <x:v>Cruise operators reap benefits of their own private islands</x:v>
-      </x:c>
-      <x:c r="D44" t="str">
-        <x:v>Reuters</x:v>
-      </x:c>
-      <x:c r="E44" t="str">
-        <x:v>https://www.reuters.com/business/autos-transportation/cruise-operators-reap-benefits-their-own-private-islands-2024-10-29/</x:v>
-      </x:c>
-      <x:c r="F44" t="str">
-        <x:v>Private destinations are reshaping cruise investment, revenue capture and Caribbean call patterns.</x:v>
-      </x:c>
-      <x:c r="G44" t="str">
-        <x:v>Caribbean</x:v>
-      </x:c>
-      <x:c r="H44" t="str">
-        <x:v>Regional</x:v>
-      </x:c>
-      <x:c r="I44" t="str">
-        <x:v>Cruise / tourism</x:v>
-      </x:c>
-      <x:c r="J44" t="str">
-        <x:v>Strategic investment</x:v>
-      </x:c>
-      <x:c r="K44" t="str">
-        <x:v>Private destination expansion</x:v>
-      </x:c>
-      <x:c r="L44" t="str">
-        <x:v>EVT133_003</x:v>
-      </x:c>
-      <x:c r="M44" t="str">
-        <x:v>Verified</x:v>
-      </x:c>
-      <x:c r="N44" t="str">
-        <x:v>SRC133_003</x:v>
-      </x:c>
-      <x:c r="O44" t="str"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="str">
-        <x:v>NEWS134_001</x:v>
-      </x:c>
-      <x:c r="B45" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C45" t="str">
-        <x:v>Oil Tanker Company Says It’s Owed $55 Million in Rate Dispute</x:v>
-      </x:c>
-      <x:c r="D45" t="str">
-        <x:v>gCaptain</x:v>
-      </x:c>
-      <x:c r="E45" t="str">
-        <x:v>https://gcaptain.com/oil-tanker-company-says-its-owed-55-million-in-rate-dispute/</x:v>
-      </x:c>
-      <x:c r="F45" t="str">
-        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
-      </x:c>
-      <x:c r="G45" t="str">
-        <x:v>Middle East / Global</x:v>
-      </x:c>
-      <x:c r="H45" t="str"/>
-      <x:c r="I45" t="str">
-        <x:v>Tankers / freight markets</x:v>
-      </x:c>
-      <x:c r="J45" t="str">
-        <x:v>Commercial / legal dispute</x:v>
-      </x:c>
-      <x:c r="K45" t="str">
-        <x:v>Rate benchmark / receivable</x:v>
-      </x:c>
-      <x:c r="L45" t="str">
-        <x:v>EVT134_001</x:v>
-      </x:c>
-      <x:c r="M45" t="str">
-        <x:v>Reported / pending adjudication</x:v>
-      </x:c>
-      <x:c r="N45" t="str">
-        <x:v>SRC134_003</x:v>
-      </x:c>
-      <x:c r="O45" t="str">
-        <x:v>Counterparty undisclosed in current article; Mercuria appeared in earlier company reporting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="str">
-        <x:v>NEWS134_002</x:v>
-      </x:c>
-      <x:c r="B46" t="str"/>
-      <x:c r="C46" t="str">
-        <x:v>Seaspan awarded a submarine maintenance contract extension by Babcock Canada through 2032</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
-        <x:v>Seaspan</x:v>
-      </x:c>
-      <x:c r="E46" t="str">
-        <x:v>https://www.seaspan.com/press-release/seaspan-awarded-a-submarine-maintenance-contract-extension-by-babcock-canada-through-2032/</x:v>
-      </x:c>
-      <x:c r="F46" t="str">
-        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
-      </x:c>
-      <x:c r="G46" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="H46" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="I46" t="str">
-        <x:v>Defence shipbuilding / MRO</x:v>
-      </x:c>
-      <x:c r="J46" t="str">
-        <x:v>Contract extension</x:v>
-      </x:c>
-      <x:c r="K46" t="str">
-        <x:v>Submarine maintenance</x:v>
-      </x:c>
-      <x:c r="L46" t="str">
-        <x:v>EVT134_002</x:v>
-      </x:c>
-      <x:c r="M46" t="str">
-        <x:v>Official headline verified; value and announcement date not captured</x:v>
-      </x:c>
-      <x:c r="N46" t="str">
-        <x:v>SRC134_004</x:v>
-      </x:c>
-      <x:c r="O46" t="str">
-        <x:v>Do not infer contract value or expanded scope beyond the source headline.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="B47" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C47" t="str">
-        <x:v>MSC Shipmanagement Fined $1.75 Million Over Illegal Oily Waste Discharges</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>gCaptain</x:v>
-      </x:c>
-      <x:c r="E47" t="str">
-        <x:v>https://gcaptain.com/msc-shipmanagement-fined-1-75-million-over-illegal-oily-waste-discharges/</x:v>
-      </x:c>
-      <x:c r="F47" t="str">
-        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
-      </x:c>
-      <x:c r="G47" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="H47" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="I47" t="str">
-        <x:v>Shipping / environmental compliance</x:v>
-      </x:c>
-      <x:c r="J47" t="str">
-        <x:v>Enforcement</x:v>
-      </x:c>
-      <x:c r="K47" t="str">
-        <x:v>MARPOL / APPS oily-waste discharge</x:v>
-      </x:c>
-      <x:c r="L47" t="str">
-        <x:v>EVT134_003</x:v>
-      </x:c>
-      <x:c r="M47" t="str">
-        <x:v>Guilty pleas / court order reported</x:v>
-      </x:c>
-      <x:c r="N47" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-      <x:c r="O47" t="str">
-        <x:v>Vessel identifiers beyond name require registry verification.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" t="str">
-        <x:v>NEWS134_004</x:v>
-      </x:c>
-      <x:c r="B48" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C48" t="str">
-        <x:v>U.S. Adds 16 Maritime Training Centers Amid Shipbuilding Push</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
-        <x:v>gCaptain</x:v>
-      </x:c>
-      <x:c r="E48" t="str">
-        <x:v>https://gcaptain.com/u-s-adds-16-maritime-training-centers-amid-shipbuilding-push/</x:v>
-      </x:c>
-      <x:c r="F48" t="str">
-        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
-      </x:c>
-      <x:c r="G48" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="H48" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="I48" t="str">
-        <x:v>Maritime workforce / shipbuilding</x:v>
-      </x:c>
-      <x:c r="J48" t="str">
-        <x:v>Programme expansion</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
-        <x:v>Training-center designations</x:v>
-      </x:c>
-      <x:c r="L48" t="str">
-        <x:v>EVT134_004</x:v>
-      </x:c>
-      <x:c r="M48" t="str">
-        <x:v>Reported from MARAD programme information</x:v>
-      </x:c>
-      <x:c r="N48" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="O48" t="str">
-        <x:v>Five institutions named in source captured; full 16-institution roster remains a research item.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="str">
-        <x:v>NEWS134_005</x:v>
-      </x:c>
-      <x:c r="B49" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="C49" t="str">
-        <x:v>Russia's Arctic LNG 2 Seeks $1 Billion in Damages From South Korea's Hanwha</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
-        <x:v>Reuters / gCaptain</x:v>
-      </x:c>
-      <x:c r="E49" t="str">
-        <x:v>https://gcaptain.com/russias-arctic-lng-2-seeks-1-billion-in-damages-from-south-koreas-hanwha/</x:v>
-      </x:c>
-      <x:c r="F49" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
-      </x:c>
-      <x:c r="G49" t="str">
-        <x:v>Arctic / Asia</x:v>
-      </x:c>
-      <x:c r="H49" t="str">
-        <x:v>Russia / South Korea</x:v>
-      </x:c>
-      <x:c r="I49" t="str">
-        <x:v>LNG / shipbuilding</x:v>
-      </x:c>
-      <x:c r="J49" t="str">
-        <x:v>Commercial / legal dispute</x:v>
-      </x:c>
-      <x:c r="K49" t="str">
-        <x:v>Shipbuilding arbitration</x:v>
-      </x:c>
-      <x:c r="L49" t="str">
-        <x:v>EVT134_005</x:v>
-      </x:c>
-      <x:c r="M49" t="str">
-        <x:v>Reported / pending arbitration</x:v>
-      </x:c>
-      <x:c r="N49" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="O49" t="str">
-        <x:v>Sanctions and canceled carrier orders are central context.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7926,19 +7070,19 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="14" t="str">
-        <x:v>NLINK00048</x:v>
+        <x:v>NLINKV12507</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
-        <x:v>NEWS00021</x:v>
+        <x:v>NEWSV12503</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
+        <x:v>COMP_QUBE</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
-        <x:v>INVESTOR</x:v>
+        <x:v>TARGET</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7946,25 +7090,23 @@
       <x:c r="G48" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="H48" s="14" t="str">
-        <x:v>Gulftainer</x:v>
-      </x:c>
+      <x:c r="H48" s="14"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="14" t="str">
-        <x:v>NLINK00049</x:v>
+        <x:v>NLINKV1251_001</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
-        <x:v>NEWS00021</x:v>
+        <x:v>NEWSV1251_01</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>COMP_SUKSAWAT_TERMINAL</x:v>
+        <x:v>COMP_DAVIE</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
-        <x:v>TARGET / OPERATING PLATFORM</x:v>
+        <x:v>SUBJECT</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7973,24 +7115,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
-        <x:v>Suksawat Terminal Co.</x:v>
+        <x:v>Davie contract award</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="14" t="str">
-        <x:v>NLINK00050</x:v>
+        <x:v>NLINKV1251_002</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>NEWS00021</x:v>
+        <x:v>NEWSV1251_01</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>TERM0530</x:v>
+        <x:v>COMP_INOCEA</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>Terminal</x:v>
+        <x:v>Company</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>TARGET ASSET</x:v>
+        <x:v>PARENT</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
         <x:v>Primary</x:v>
@@ -7999,24 +7141,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>Suksawat Terminal</x:v>
+        <x:v>Inocea parent group</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="14" t="str">
-        <x:v>NLINK00051</x:v>
+        <x:v>NLINKV1251_003</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
-        <x:v>NEWS00022</x:v>
+        <x:v>NEWSV1251_02</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
+        <x:v>COMP_DAVIE_DEFENSE</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>INVESTOR</x:v>
+        <x:v>BUYER</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
         <x:v>Primary</x:v>
@@ -8025,24 +7167,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>Gulftainer</x:v>
+        <x:v>U.S. acquisition vehicle</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
-        <x:v>NLINK00052</x:v>
+        <x:v>NLINKV1251_004</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>NEWS00022</x:v>
+        <x:v>NEWSV1251_02</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>TERM0530</x:v>
+        <x:v>COMP_GULF_COPPER</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>Terminal</x:v>
+        <x:v>Company</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>TARGET ASSET</x:v>
+        <x:v>TARGET / ASSET</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
         <x:v>Primary</x:v>
@@ -8051,44 +7193,44 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
-        <x:v>Suksawat Terminal</x:v>
+        <x:v>Texas shipyard group</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
-        <x:v>NLINK00053</x:v>
+        <x:v>NLINKV1251_005</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>NEWS00023</x:v>
+        <x:v>NEWSV1251_02</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
+        <x:v>COMP_INOCEA</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>SUBJECT</x:v>
+        <x:v>PARENT</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>Primary</x:v>
+        <x:v>Secondary</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>Global strategy</x:v>
+        <x:v>Parent group</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="14" t="str">
-        <x:v>NLINK00054</x:v>
+        <x:v>NLINKV1251_006</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
-        <x:v>NEWS00024</x:v>
+        <x:v>NEWSV1251_03</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
+        <x:v>COMP_SEASPAN_CORP</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
         <x:v>Company</x:v>
@@ -8103,24 +7245,24 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str">
-        <x:v>GT Lines / Iraq corridor</x:v>
+        <x:v>Fleet owner</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="14" t="str">
-        <x:v>NLINK00055</x:v>
+        <x:v>NLINKV1251_007</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
-        <x:v>NEWS00025</x:v>
+        <x:v>NEWSV1251_03</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>COMP_GULFTAINER</x:v>
+        <x:v>COMP_MAERSK</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
         <x:v>Company</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>SUBJECT</x:v>
+        <x:v>CHARTER PARTNER</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
         <x:v>Primary</x:v>
@@ -8129,7 +7271,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str">
-        <x:v>Al Dhaid corridor</x:v>
+        <x:v>Charterer</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -9405,514 +8547,6 @@
       <x:c r="H104" t="str">
         <x:v>Persian Gulf / Hormuz / Gulf of Oman Security System</x:v>
       </x:c>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" t="str">
-        <x:v>NL133_001</x:v>
-      </x:c>
-      <x:c r="B105" t="str">
-        <x:v>NEWS133_001</x:v>
-      </x:c>
-      <x:c r="C105" t="str">
-        <x:v>VES_HERCULES_STAR</x:v>
-      </x:c>
-      <x:c r="D105" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E105" t="str">
-        <x:v>SUBJECT</x:v>
-      </x:c>
-      <x:c r="F105" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G105" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H105" t="str"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" t="str">
-        <x:v>NL133_002</x:v>
-      </x:c>
-      <x:c r="B106" t="str">
-        <x:v>NEWS133_001</x:v>
-      </x:c>
-      <x:c r="C106" t="str">
-        <x:v>COMP_PENINSULA</x:v>
-      </x:c>
-      <x:c r="D106" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E106" t="str">
-        <x:v>CHARTERER</x:v>
-      </x:c>
-      <x:c r="F106" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G106" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H106" t="str"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" t="str">
-        <x:v>NL133_003</x:v>
-      </x:c>
-      <x:c r="B107" t="str">
-        <x:v>NEWS133_001</x:v>
-      </x:c>
-      <x:c r="C107" t="str">
-        <x:v>COMP_HERCULES_TANKER</x:v>
-      </x:c>
-      <x:c r="D107" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E107" t="str">
-        <x:v>SISTER COMPANY / VESSEL PROVIDER</x:v>
-      </x:c>
-      <x:c r="F107" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G107" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H107" t="str"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" t="str">
-        <x:v>NL133_004</x:v>
-      </x:c>
-      <x:c r="B108" t="str">
-        <x:v>NEWS133_002</x:v>
-      </x:c>
-      <x:c r="C108" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
-      </x:c>
-      <x:c r="D108" t="str">
-        <x:v>Port</x:v>
-      </x:c>
-      <x:c r="E108" t="str">
-        <x:v>OPENED PORT</x:v>
-      </x:c>
-      <x:c r="F108" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G108" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H108" t="str">
-        <x:v>Headline-level record.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109">
-      <x:c r="A109" t="str">
-        <x:v>NL133_005</x:v>
-      </x:c>
-      <x:c r="B109" t="str">
-        <x:v>NEWS133_002</x:v>
-      </x:c>
-      <x:c r="C109" t="str">
-        <x:v>ORG_NISGAA_NATION</x:v>
-      </x:c>
-      <x:c r="D109" t="str">
-        <x:v>Organization</x:v>
-      </x:c>
-      <x:c r="E109" t="str">
-        <x:v>OPENING PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="F109" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G109" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H109" t="str"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" t="str">
-        <x:v>NL133_006</x:v>
-      </x:c>
-      <x:c r="B110" t="str">
-        <x:v>NEWS133_002</x:v>
-      </x:c>
-      <x:c r="C110" t="str">
-        <x:v>ORG_TAHLTAN_NATION</x:v>
-      </x:c>
-      <x:c r="D110" t="str">
-        <x:v>Organization</x:v>
-      </x:c>
-      <x:c r="E110" t="str">
-        <x:v>OPENING PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="F110" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G110" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H110" t="str"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" t="str">
-        <x:v>NL133_007</x:v>
-      </x:c>
-      <x:c r="B111" t="str">
-        <x:v>NEWS133_003</x:v>
-      </x:c>
-      <x:c r="C111" t="str">
-        <x:v>COMP_ROYAL_CARIBBEAN_GROUP</x:v>
-      </x:c>
-      <x:c r="D111" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E111" t="str">
-        <x:v>SECTOR PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="F111" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G111" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H111" t="str"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="A112" t="str">
-        <x:v>NL133_008</x:v>
-      </x:c>
-      <x:c r="B112" t="str">
-        <x:v>NEWS133_003</x:v>
-      </x:c>
-      <x:c r="C112" t="str">
-        <x:v>COMP_CARNIVAL_CORP</x:v>
-      </x:c>
-      <x:c r="D112" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E112" t="str">
-        <x:v>SECTOR PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="F112" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G112" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H112" t="str"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="A113" t="str">
-        <x:v>NL133_009</x:v>
-      </x:c>
-      <x:c r="B113" t="str">
-        <x:v>NEWS133_003</x:v>
-      </x:c>
-      <x:c r="C113" t="str">
-        <x:v>COMP_NCLH</x:v>
-      </x:c>
-      <x:c r="D113" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E113" t="str">
-        <x:v>SECTOR PARTICIPANT</x:v>
-      </x:c>
-      <x:c r="F113" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G113" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H113" t="str"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="A114" t="str">
-        <x:v>NL134_001</x:v>
-      </x:c>
-      <x:c r="B114" t="str">
-        <x:v>NEWS134_001</x:v>
-      </x:c>
-      <x:c r="C114" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
-      </x:c>
-      <x:c r="D114" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E114" t="str">
-        <x:v>CLAIMANT</x:v>
-      </x:c>
-      <x:c r="F114" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G114" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H114" t="str"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="A115" t="str">
-        <x:v>NL134_002</x:v>
-      </x:c>
-      <x:c r="B115" t="str">
-        <x:v>NEWS134_001</x:v>
-      </x:c>
-      <x:c r="C115" t="str">
-        <x:v>COMP_MERCURIA</x:v>
-      </x:c>
-      <x:c r="D115" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E115" t="str">
-        <x:v>REPORTED EARLIER COUNTERPARTY</x:v>
-      </x:c>
-      <x:c r="F115" t="str">
-        <x:v>Context</x:v>
-      </x:c>
-      <x:c r="G115" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="H115" t="str">
-        <x:v>Current article does not disclose the counterparty.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" t="str">
-        <x:v>NL134_003</x:v>
-      </x:c>
-      <x:c r="B116" t="str">
-        <x:v>NEWS134_002</x:v>
-      </x:c>
-      <x:c r="C116" t="str">
-        <x:v>COMP_SEASPAN_ULC</x:v>
-      </x:c>
-      <x:c r="D116" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E116" t="str">
-        <x:v>CONTRACTOR</x:v>
-      </x:c>
-      <x:c r="F116" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G116" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H116" t="str"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" t="str">
-        <x:v>NL134_004</x:v>
-      </x:c>
-      <x:c r="B117" t="str">
-        <x:v>NEWS134_002</x:v>
-      </x:c>
-      <x:c r="C117" t="str">
-        <x:v>COMP_BABCOCK_CANADA</x:v>
-      </x:c>
-      <x:c r="D117" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E117" t="str">
-        <x:v>PRIME CONTRACTOR / CUSTOMER</x:v>
-      </x:c>
-      <x:c r="F117" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G117" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H117" t="str"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" t="str">
-        <x:v>NL134_005</x:v>
-      </x:c>
-      <x:c r="B118" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="C118" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
-      </x:c>
-      <x:c r="D118" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="E118" t="str">
-        <x:v>SUBJECT</x:v>
-      </x:c>
-      <x:c r="F118" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G118" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H118" t="str"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="A119" t="str">
-        <x:v>NL134_006</x:v>
-      </x:c>
-      <x:c r="B119" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="C119" t="str">
-        <x:v>COMP_MSC_SHIPMANAGEMENT</x:v>
-      </x:c>
-      <x:c r="D119" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E119" t="str">
-        <x:v>DEFENDANT / MANAGER</x:v>
-      </x:c>
-      <x:c r="F119" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G119" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H119" t="str"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="A120" t="str">
-        <x:v>NL134_007</x:v>
-      </x:c>
-      <x:c r="B120" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="C120" t="str">
-        <x:v>COMP_HONG_KONG_SPIRIT</x:v>
-      </x:c>
-      <x:c r="D120" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E120" t="str">
-        <x:v>DEFENDANT / OWNER</x:v>
-      </x:c>
-      <x:c r="F120" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G120" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H120" t="str"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="A121" t="str">
-        <x:v>NL134_008</x:v>
-      </x:c>
-      <x:c r="B121" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="C121" t="str">
-        <x:v>ORG_USCG</x:v>
-      </x:c>
-      <x:c r="D121" t="str">
-        <x:v>Government agency</x:v>
-      </x:c>
-      <x:c r="E121" t="str">
-        <x:v>INVESTIGATOR</x:v>
-      </x:c>
-      <x:c r="F121" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G121" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H121" t="str"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="A122" t="str">
-        <x:v>NL134_009</x:v>
-      </x:c>
-      <x:c r="B122" t="str">
-        <x:v>NEWS134_004</x:v>
-      </x:c>
-      <x:c r="C122" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="D122" t="str">
-        <x:v>Government agency</x:v>
-      </x:c>
-      <x:c r="E122" t="str">
-        <x:v>PROGRAMME OWNER</x:v>
-      </x:c>
-      <x:c r="F122" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G122" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H122" t="str"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="A123" t="str">
-        <x:v>NL134_010</x:v>
-      </x:c>
-      <x:c r="B123" t="str">
-        <x:v>NEWS134_005</x:v>
-      </x:c>
-      <x:c r="C123" t="str">
-        <x:v>COMP_ARCTIC_LNG2</x:v>
-      </x:c>
-      <x:c r="D123" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E123" t="str">
-        <x:v>CLAIMANT</x:v>
-      </x:c>
-      <x:c r="F123" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G123" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H123" t="str"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="A124" t="str">
-        <x:v>NL134_011</x:v>
-      </x:c>
-      <x:c r="B124" t="str">
-        <x:v>NEWS134_005</x:v>
-      </x:c>
-      <x:c r="C124" t="str">
-        <x:v>COMP_HANWHA_OCEAN</x:v>
-      </x:c>
-      <x:c r="D124" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E124" t="str">
-        <x:v>RESPONDENT</x:v>
-      </x:c>
-      <x:c r="F124" t="str">
-        <x:v>Primary</x:v>
-      </x:c>
-      <x:c r="G124" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H124" t="str"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="A125" t="str">
-        <x:v>NL134_012</x:v>
-      </x:c>
-      <x:c r="B125" t="str">
-        <x:v>NEWS134_005</x:v>
-      </x:c>
-      <x:c r="C125" t="str">
-        <x:v>COMP_NOVATEK</x:v>
-      </x:c>
-      <x:c r="D125" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="E125" t="str">
-        <x:v>PROJECT LEAD</x:v>
-      </x:c>
-      <x:c r="F125" t="str">
-        <x:v>Context</x:v>
-      </x:c>
-      <x:c r="G125" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H125" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52257,571 +50891,6 @@
         <x:v>Implementation status should be checked against primary Korean government sources before canonical ownership/governance overwrite.</x:v>
       </x:c>
     </x:row>
-    <x:row r="613">
-      <x:c r="A613" t="str">
-        <x:v>OBS_000612</x:v>
-      </x:c>
-      <x:c r="B613" t="str">
-        <x:v>EVT133_001</x:v>
-      </x:c>
-      <x:c r="C613" t="str">
-        <x:v>news_intake_v1_33</x:v>
-      </x:c>
-      <x:c r="D613" t="str">
-        <x:v>NEWS133_001</x:v>
-      </x:c>
-      <x:c r="E613" t="str">
-        <x:v>2026-09-09</x:v>
-      </x:c>
-      <x:c r="F613" t="str">
-        <x:v>Conflict / Security</x:v>
-      </x:c>
-      <x:c r="G613" t="str">
-        <x:v>Vessel incident</x:v>
-      </x:c>
-      <x:c r="H613" t="str">
-        <x:v>Suspected projectile / taking water report</x:v>
-      </x:c>
-      <x:c r="I613" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J613" t="str">
-        <x:v>Persian Gulf</x:v>
-      </x:c>
-      <x:c r="K613" t="str">
-        <x:v>United Arab Emirates</x:v>
-      </x:c>
-      <x:c r="L613" t="str">
-        <x:v>Anchorage off Dubai</x:v>
-      </x:c>
-      <x:c r="M613" t="str"/>
-      <x:c r="N613" t="str"/>
-      <x:c r="O613" t="str">
-        <x:v>HERCULES STAR</x:v>
-      </x:c>
-      <x:c r="P613" t="str">
-        <x:v>9916135</x:v>
-      </x:c>
-      <x:c r="Q613" t="str">
-        <x:v>Product tanker</x:v>
-      </x:c>
-      <x:c r="R613" t="str">
-        <x:v>Unknown / unconfirmed</x:v>
-      </x:c>
-      <x:c r="S613" t="str">
-        <x:v>Peninsula confirmed a fatal incident involving HERCULES STAR. A nearby UKMTO projectile report was cited but not conclusively matched.</x:v>
-      </x:c>
-      <x:c r="T613" t="str">
-        <x:v>One fatality; one missing; other crew accounted for</x:v>
-      </x:c>
-      <x:c r="U613" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V613" t="str"/>
-      <x:c r="W613" t="str">
-        <x:v>Emergency response and casualty investigation</x:v>
-      </x:c>
-      <x:c r="X613" t="str">
-        <x:v>Bunker tanker / anchorage risk</x:v>
-      </x:c>
-      <x:c r="Y613" t="str">
-        <x:v>Critical</x:v>
-      </x:c>
-      <x:c r="Z613" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA613" t="str">
-        <x:v>SRC133_001</x:v>
-      </x:c>
-      <x:c r="AB613" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC613" t="str">
-        <x:v>Separate from the 1 Mar 2026 minor-damage observation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="614">
-      <x:c r="A614" t="str">
-        <x:v>OBS_000613</x:v>
-      </x:c>
-      <x:c r="B614" t="str">
-        <x:v>EVT133_002</x:v>
-      </x:c>
-      <x:c r="C614" t="str">
-        <x:v>news_intake_v1_33</x:v>
-      </x:c>
-      <x:c r="D614" t="str">
-        <x:v>NEWS133_002</x:v>
-      </x:c>
-      <x:c r="E614" t="str">
-        <x:v>2026-09-10</x:v>
-      </x:c>
-      <x:c r="F614" t="str">
-        <x:v>Infrastructure / Commercial</x:v>
-      </x:c>
-      <x:c r="G614" t="str">
-        <x:v>Port opening</x:v>
-      </x:c>
-      <x:c r="H614" t="str">
-        <x:v>Expansion planning</x:v>
-      </x:c>
-      <x:c r="I614" t="str">
-        <x:v>Port</x:v>
-      </x:c>
-      <x:c r="J614" t="str">
-        <x:v>North America</x:v>
-      </x:c>
-      <x:c r="K614" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="L614" t="str">
-        <x:v>Stewart, British Columbia</x:v>
-      </x:c>
-      <x:c r="M614" t="str"/>
-      <x:c r="N614" t="str"/>
-      <x:c r="O614" t="str">
-        <x:v>Port of Stewart</x:v>
-      </x:c>
-      <x:c r="P614" t="str">
-        <x:v>PORT_STEWART_BC</x:v>
-      </x:c>
-      <x:c r="Q614" t="str">
-        <x:v>Port / harbour</x:v>
-      </x:c>
-      <x:c r="R614" t="str">
-        <x:v>Nisg̱a'a Nation; Tahltan Nation</x:v>
-      </x:c>
-      <x:c r="S614" t="str">
-        <x:v>Official opening reported with expansion plans taking shape.</x:v>
-      </x:c>
-      <x:c r="T614" t="str">
-        <x:v>New gateway / development milestone</x:v>
-      </x:c>
-      <x:c r="U614" t="str"/>
-      <x:c r="V614" t="str"/>
-      <x:c r="W614" t="str">
-        <x:v>Port opening and planned expansion</x:v>
-      </x:c>
-      <x:c r="X614" t="str">
-        <x:v>Potential northern B.C. trade and project-cargo connectivity</x:v>
-      </x:c>
-      <x:c r="Y614" t="str">
-        <x:v>Moderate</x:v>
-      </x:c>
-      <x:c r="Z614" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="AA614" t="str">
-        <x:v>SRC133_002</x:v>
-      </x:c>
-      <x:c r="AB614" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC614" t="str">
-        <x:v>Headline-level evidence only; verify operator, ownership, cargo and capacity before enrichment.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="615">
-      <x:c r="A615" t="str">
-        <x:v>OBS_000614</x:v>
-      </x:c>
-      <x:c r="B615" t="str">
-        <x:v>EVT134_001</x:v>
-      </x:c>
-      <x:c r="C615" t="str">
-        <x:v>news_intake_v1_34</x:v>
-      </x:c>
-      <x:c r="D615" t="str">
-        <x:v>NEWS134_001</x:v>
-      </x:c>
-      <x:c r="E615" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F615" t="str">
-        <x:v>Commercial / Legal</x:v>
-      </x:c>
-      <x:c r="G615" t="str">
-        <x:v>Commercial / legal dispute</x:v>
-      </x:c>
-      <x:c r="H615" t="str">
-        <x:v>Rate benchmark / receivable</x:v>
-      </x:c>
-      <x:c r="I615" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J615" t="str">
-        <x:v>Persian Gulf / Global</x:v>
-      </x:c>
-      <x:c r="K615" t="str"/>
-      <x:c r="L615" t="str">
-        <x:v>Tanker rate market</x:v>
-      </x:c>
-      <x:c r="M615" t="str"/>
-      <x:c r="N615" t="str"/>
-      <x:c r="O615" t="str">
-        <x:v>Hunter Group ASA</x:v>
-      </x:c>
-      <x:c r="P615" t="str">
-        <x:v>COMP_HUNTER_GROUP</x:v>
-      </x:c>
-      <x:c r="Q615" t="str">
-        <x:v>Company</x:v>
-      </x:c>
-      <x:c r="R615" t="str">
-        <x:v>Hunter Group / undisclosed counterparty</x:v>
-      </x:c>
-      <x:c r="S615" t="str">
-        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
-      </x:c>
-      <x:c r="T615" t="str">
-        <x:v>Pending court dispute</x:v>
-      </x:c>
-      <x:c r="U615" t="str"/>
-      <x:c r="V615" t="str"/>
-      <x:c r="W615" t="str">
-        <x:v>Hunter Group reports a USD 55m underpayment claim amid disputed wartime tanker benchmarks.</x:v>
-      </x:c>
-      <x:c r="X615" t="str">
-        <x:v>Tanker rate and receivable risk</x:v>
-      </x:c>
-      <x:c r="Y615" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="Z615" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA615" t="str">
-        <x:v>SRC134_003</x:v>
-      </x:c>
-      <x:c r="AB615" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC615" t="str">
-        <x:v>Counterparty undisclosed in current article; Mercuria appeared in earlier company reporting.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="616">
-      <x:c r="A616" t="str">
-        <x:v>OBS_000615</x:v>
-      </x:c>
-      <x:c r="B616" t="str">
-        <x:v>EVT134_002</x:v>
-      </x:c>
-      <x:c r="C616" t="str">
-        <x:v>news_intake_v1_34</x:v>
-      </x:c>
-      <x:c r="D616" t="str">
-        <x:v>NEWS134_002</x:v>
-      </x:c>
-      <x:c r="E616" t="str"/>
-      <x:c r="F616" t="str">
-        <x:v>Defence / Industrial</x:v>
-      </x:c>
-      <x:c r="G616" t="str">
-        <x:v>Contract extension</x:v>
-      </x:c>
-      <x:c r="H616" t="str">
-        <x:v>Submarine maintenance</x:v>
-      </x:c>
-      <x:c r="I616" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J616" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="K616" t="str">
-        <x:v>Canada</x:v>
-      </x:c>
-      <x:c r="L616" t="str">
-        <x:v>Victoria, British Columbia</x:v>
-      </x:c>
-      <x:c r="M616" t="str"/>
-      <x:c r="N616" t="str"/>
-      <x:c r="O616" t="str">
-        <x:v>Victoria-class submarine support</x:v>
-      </x:c>
-      <x:c r="P616" t="str">
-        <x:v>PROG_SEA_VISSC</x:v>
-      </x:c>
-      <x:c r="Q616" t="str">
-        <x:v>Defence programme</x:v>
-      </x:c>
-      <x:c r="R616" t="str">
-        <x:v>Seaspan / Babcock Canada</x:v>
-      </x:c>
-      <x:c r="S616" t="str">
-        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
-      </x:c>
-      <x:c r="T616" t="str">
-        <x:v>Extension through 2032</x:v>
-      </x:c>
-      <x:c r="U616" t="str"/>
-      <x:c r="V616" t="str"/>
-      <x:c r="W616" t="str">
-        <x:v>Official headline confirms a Victoria-class submarine maintenance support extension through 2032.</x:v>
-      </x:c>
-      <x:c r="X616" t="str">
-        <x:v>Canadian submarine MRO continuity</x:v>
-      </x:c>
-      <x:c r="Y616" t="str">
-        <x:v>Moderate</x:v>
-      </x:c>
-      <x:c r="Z616" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA616" t="str">
-        <x:v>SRC134_004</x:v>
-      </x:c>
-      <x:c r="AB616" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC616" t="str">
-        <x:v>Do not infer contract value or expanded scope beyond the source headline.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="617">
-      <x:c r="A617" t="str">
-        <x:v>OBS_000616</x:v>
-      </x:c>
-      <x:c r="B617" t="str">
-        <x:v>EVT134_003</x:v>
-      </x:c>
-      <x:c r="C617" t="str">
-        <x:v>news_intake_v1_34</x:v>
-      </x:c>
-      <x:c r="D617" t="str">
-        <x:v>NEWS134_003</x:v>
-      </x:c>
-      <x:c r="E617" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F617" t="str">
-        <x:v>Regulatory / Enforcement</x:v>
-      </x:c>
-      <x:c r="G617" t="str">
-        <x:v>Enforcement</x:v>
-      </x:c>
-      <x:c r="H617" t="str">
-        <x:v>MARPOL / APPS oily-waste discharge</x:v>
-      </x:c>
-      <x:c r="I617" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J617" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="K617" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="L617" t="str">
-        <x:v>Port of Philadelphia / Delaware River</x:v>
-      </x:c>
-      <x:c r="M617" t="str"/>
-      <x:c r="N617" t="str"/>
-      <x:c r="O617" t="str">
-        <x:v>MSC SAMIRA III</x:v>
-      </x:c>
-      <x:c r="P617" t="str">
-        <x:v>VES_MSC_SAMIRA_III</x:v>
-      </x:c>
-      <x:c r="Q617" t="str">
-        <x:v>Vessel</x:v>
-      </x:c>
-      <x:c r="R617" t="str">
-        <x:v>MSC Shipmanagement / Hong Kong Spirit</x:v>
-      </x:c>
-      <x:c r="S617" t="str">
-        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
-      </x:c>
-      <x:c r="T617" t="str">
-        <x:v>USD 1.75m combined fine; four years' probation each</x:v>
-      </x:c>
-      <x:c r="U617" t="str"/>
-      <x:c r="V617" t="str"/>
-      <x:c r="W617" t="str">
-        <x:v>MSC Shipmanagement and the vessel owner received a combined USD 1.75m fine and four years' probation each.</x:v>
-      </x:c>
-      <x:c r="X617" t="str">
-        <x:v>Environmental-compliance and reputational exposure</x:v>
-      </x:c>
-      <x:c r="Y617" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="Z617" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA617" t="str">
-        <x:v>SRC134_005</x:v>
-      </x:c>
-      <x:c r="AB617" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC617" t="str">
-        <x:v>Vessel identifiers beyond name require registry verification.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="618">
-      <x:c r="A618" t="str">
-        <x:v>OBS_000617</x:v>
-      </x:c>
-      <x:c r="B618" t="str">
-        <x:v>EVT134_004</x:v>
-      </x:c>
-      <x:c r="C618" t="str">
-        <x:v>news_intake_v1_34</x:v>
-      </x:c>
-      <x:c r="D618" t="str">
-        <x:v>NEWS134_004</x:v>
-      </x:c>
-      <x:c r="E618" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F618" t="str">
-        <x:v>Workforce / Industrial Capacity</x:v>
-      </x:c>
-      <x:c r="G618" t="str">
-        <x:v>Programme expansion</x:v>
-      </x:c>
-      <x:c r="H618" t="str">
-        <x:v>Training-center designations</x:v>
-      </x:c>
-      <x:c r="I618" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J618" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="K618" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="L618" t="str">
-        <x:v>United States</x:v>
-      </x:c>
-      <x:c r="M618" t="str"/>
-      <x:c r="N618" t="str"/>
-      <x:c r="O618" t="str">
-        <x:v>Maritime workforce training network</x:v>
-      </x:c>
-      <x:c r="P618" t="str">
-        <x:v>ORG_MARAD</x:v>
-      </x:c>
-      <x:c r="Q618" t="str">
-        <x:v>Training programme</x:v>
-      </x:c>
-      <x:c r="R618" t="str">
-        <x:v>MARAD</x:v>
-      </x:c>
-      <x:c r="S618" t="str">
-        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
-      </x:c>
-      <x:c r="T618" t="str">
-        <x:v>16 additional institutions designated</x:v>
-      </x:c>
-      <x:c r="U618" t="str"/>
-      <x:c r="V618" t="str"/>
-      <x:c r="W618" t="str">
-        <x:v>MARAD added 16 institutions to the maritime workforce network, which now spans 48 institutions and 87 facilities.</x:v>
-      </x:c>
-      <x:c r="X618" t="str">
-        <x:v>Workforce capacity for shipbuilding and mariner supply</x:v>
-      </x:c>
-      <x:c r="Y618" t="str">
-        <x:v>Moderate</x:v>
-      </x:c>
-      <x:c r="Z618" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA618" t="str">
-        <x:v>SRC134_006</x:v>
-      </x:c>
-      <x:c r="AB618" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC618" t="str">
-        <x:v>Five institutions named in source captured; full 16-institution roster remains a research item.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="619">
-      <x:c r="A619" t="str">
-        <x:v>OBS_000618</x:v>
-      </x:c>
-      <x:c r="B619" t="str">
-        <x:v>EVT134_005</x:v>
-      </x:c>
-      <x:c r="C619" t="str">
-        <x:v>news_intake_v1_34</x:v>
-      </x:c>
-      <x:c r="D619" t="str">
-        <x:v>NEWS134_005</x:v>
-      </x:c>
-      <x:c r="E619" t="str">
-        <x:v>2026-09-08</x:v>
-      </x:c>
-      <x:c r="F619" t="str">
-        <x:v>Commercial / Legal</x:v>
-      </x:c>
-      <x:c r="G619" t="str">
-        <x:v>Commercial / legal dispute</x:v>
-      </x:c>
-      <x:c r="H619" t="str">
-        <x:v>Shipbuilding arbitration</x:v>
-      </x:c>
-      <x:c r="I619" t="str">
-        <x:v>Maritime</x:v>
-      </x:c>
-      <x:c r="J619" t="str">
-        <x:v>Russian Arctic / South Korea</x:v>
-      </x:c>
-      <x:c r="K619" t="str">
-        <x:v>Russia / South Korea</x:v>
-      </x:c>
-      <x:c r="L619" t="str">
-        <x:v>Singapore arbitration / Geoje shipbuilding</x:v>
-      </x:c>
-      <x:c r="M619" t="str"/>
-      <x:c r="N619" t="str"/>
-      <x:c r="O619" t="str">
-        <x:v>Arctic LNG 2 Arc7 carrier programme</x:v>
-      </x:c>
-      <x:c r="P619" t="str">
-        <x:v>PROG_ARCTIC_LNG2_ARC7</x:v>
-      </x:c>
-      <x:c r="Q619" t="str">
-        <x:v>Shipbuilding programme</x:v>
-      </x:c>
-      <x:c r="R619" t="str">
-        <x:v>Arctic LNG 2 / Hanwha Ocean</x:v>
-      </x:c>
-      <x:c r="S619" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
-      </x:c>
-      <x:c r="T619" t="str">
-        <x:v>USD 1.02bn claim filed at SIAC</x:v>
-      </x:c>
-      <x:c r="U619" t="str"/>
-      <x:c r="V619" t="str"/>
-      <x:c r="W619" t="str">
-        <x:v>Arctic LNG 2 seeks USD 1.02bn at SIAC over terminated contracts for Arc7 LNG carriers.</x:v>
-      </x:c>
-      <x:c r="X619" t="str">
-        <x:v>Arctic LNG export-fleet and sanctions risk</x:v>
-      </x:c>
-      <x:c r="Y619" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="Z619" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="AA619" t="str">
-        <x:v>SRC134_008</x:v>
-      </x:c>
-      <x:c r="AB619" t="str">
-        <x:v>Canonical event resolved</x:v>
-      </x:c>
-      <x:c r="AC619" t="str">
-        <x:v>Sanctions and canceled carrier orders are central context.</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R4095d5dfde534c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R4e635d29054d4c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R9dbee3769fb14495"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R9e3bb237fa5c41ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R8de403f624444a27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Ra54e7b8a33854cd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Rd3a69f5fc6e5401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R6785606a43c14fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R7902f67a772a44bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="Rb1cdcfd7de8c404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R1d9932f36dd644d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R8f7987f541bd4255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R8dea24e411834cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R044a1041b213498f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R4740b1f84dc14509"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Rcf9e45927b324ae6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R3f0ef2231caa4867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rc015daf5d1ca4ee2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rdbb4fbbdb99b438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R4aa0dc19e7ed4535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Ra92fc581b4a44c4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R13faa0942b2549da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R2e3c8ac9e25e480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R34d6df86b3c347a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="Ra7d60b8cbf8642e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R3d5f466278be415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R47b363e394b349ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R96c6877f0402431d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7094,6 +7094,192 @@
         <x:v>Strategically relevant to timing of Neltume's new Montevideo investment proposal.</x:v>
       </x:c>
     </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>NEWS_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>India launches advanced Ocean Research Vessel ORV Sagar Manthan</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>Press Information Bureau</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2308170&amp;lang=1&amp;reg=48</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>NCPOR/MoES launches GRSE-built Yard 3041 under Deep Ocean Mission; delivery scheduled for 2028.</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>Shipbuilding / Ocean Research</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="K61" t="str">
+        <x:v>Vessel launch / naming</x:v>
+      </x:c>
+      <x:c r="L61" t="str">
+        <x:v>EVENT_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="M61" t="str">
+        <x:v>Verified / primary</x:v>
+      </x:c>
+      <x:c r="N61" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+      <x:c r="O61" t="str">
+        <x:v>Corrects earlier secondary-source attribution to Indian Navy; this is a civilian scientific programme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>NEWS_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>GRSE signs ₹840 crore contract with NCPOR for Ocean Research Vessel</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>Government research-vessel procurement valued at ₹840 crore, approximately US$100.50m using contract-date FX.</x:v>
+      </x:c>
+      <x:c r="G62" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H62" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>Shipbuilding / Ocean Research</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>Contract award</x:v>
+      </x:c>
+      <x:c r="K62" t="str">
+        <x:v>Government research vessel</x:v>
+      </x:c>
+      <x:c r="L62" t="str">
+        <x:v>EVENT_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="M62" t="str">
+        <x:v>Verified / primary</x:v>
+      </x:c>
+      <x:c r="N62" t="str">
+        <x:v>SRC_SAGAR_GRSE_CONTRACT</x:v>
+      </x:c>
+      <x:c r="O62" t="str">
+        <x:v>Yard 3041; 89.5 m; 18.8 m beam; 5,900 GT; 14 knots; 6,000 m research depth.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>NEWS_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>GRSE signs ₹490.98 crore Acoustic Research Ship contract with NPOL</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>NPOL/DRDO orders one 90 m Acoustic Research Ship, approximately US$58.40m using contract-date FX.</x:v>
+      </x:c>
+      <x:c r="G63" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H63" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>Defence R&amp;D / Shipbuilding</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>Contract award</x:v>
+      </x:c>
+      <x:c r="K63" t="str">
+        <x:v>Acoustic research ship</x:v>
+      </x:c>
+      <x:c r="L63" t="str">
+        <x:v>EVENT_SAGAR_005</x:v>
+      </x:c>
+      <x:c r="M63" t="str">
+        <x:v>Verified / primary</x:v>
+      </x:c>
+      <x:c r="N63" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+      <x:c r="O63" t="str">
+        <x:v>Yard 3058; designed for underwater acoustic research and trials.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>NEWS_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>2025-04-16</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>GRSE starts construction of NPOL Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>https://www.grse.in/press-releases-2025-26-quarter1/</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>Construction begins on NPOL/DRDO Acoustic Research Ship, later identified in GRSE tender records as Yard 3058.</x:v>
+      </x:c>
+      <x:c r="G64" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H64" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>Defence R&amp;D / Shipbuilding</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="K64" t="str">
+        <x:v>Production start</x:v>
+      </x:c>
+      <x:c r="L64" t="str">
+        <x:v>EVENT_SAGAR_006</x:v>
+      </x:c>
+      <x:c r="M64" t="str">
+        <x:v>Verified / primary</x:v>
+      </x:c>
+      <x:c r="N64" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS_START</x:v>
+      </x:c>
+      <x:c r="O64"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10688,6 +10874,308 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>NLINK_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>NEWS_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>ORV Sagar Manthan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>NLINK_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>NEWS_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>BUILDER</x:v>
+      </x:c>
+      <x:c r="F138" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G138" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H138" t="str">
+        <x:v>GRSE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>NLINK_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>NEWS_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>Government Research Institute</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>CUSTOMER / OPERATOR</x:v>
+      </x:c>
+      <x:c r="F139" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G139" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H139" t="str">
+        <x:v>NCPOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>NLINK_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>NEWS_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>PROG_DEEP_OCEAN_MISSION</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>Programme</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>PROGRAMME</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>Deep Ocean Mission Vertical 4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>NLINK_SAGAR_005</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>NEWS_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>CONTRACTED_ASSET</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>Yard 3041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>NLINK_SAGAR_006</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>NEWS_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>CONTRACTOR</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>NLINK_SAGAR_007</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>NEWS_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>Government Research Institute</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>CUSTOMER</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>NLINK_SAGAR_008</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>NEWS_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>CONTRACTED_ASSET</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>Yard 3058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>NLINK_SAGAR_009</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>NEWS_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>CONTRACTOR</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>NLINK_SAGAR_010</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>NEWS_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>Government Defence Laboratory</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>CUSTOMER</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>NLINK_SAGAR_011</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>NEWS_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>Vessel</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>SUBJECT</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>Construction commencement</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>NLINK_SAGAR_012</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>NEWS_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>Company</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>BUILDER</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>Primary</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H148"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11764,6 +12252,198 @@
       </x:c>
       <x:c r="J33" t="str">
         <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>EVENT_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Contract award</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>NCPOR awards GRSE ₹840 crore Ocean Research Vessel contract</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Contract signed for one advanced ORV, later named ORV Sagar Manthan, Yard 3041.</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Starts domestic construction programme</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>₹840 crore; ~US$100.50m contract-date normalized</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>SRC_SAGAR_GRSE_CONTRACT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>EVENT_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>2024-11-29</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Kolkata, India</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>First steel cut for Yard 3041</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Production begins for NCPOR Ocean Research Vessel.</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Construction start</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Advances Deep Ocean Mission research-vessel capability</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>EVENT_SAGAR_003</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>2026-04-08</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Kolkata, India</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Keel laid for Yard 3041</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Keel laying for the future ORV Sagar Manthan.</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Hull construction milestone</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Launch achieved five months later</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>EVENT_SAGAR_004</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Vessel launch</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Rishi Bankim Shipyard, Kolkata</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>ORV Sagar Manthan launched and named</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Yard 3041 launched for NCPOR/MoES under Deep Ocean Mission.</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Moves to outfitting, integration and sea-trial phase</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>Delivery scheduled 2028; 30-year projected service life</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>SRC_SAGAR_PIB_LAUNCH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>EVENT_SAGAR_005</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Contract award</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>NPOL/DRDO awards GRSE Acoustic Research Ship contract</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>One 90 m Acoustic Research Ship ordered from GRSE for NPOL.</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Starts specialist defence-R&amp;D vessel programme</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>₹490.98 crore; ~US$58.40m contract-date normalized</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>EVENT_SAGAR_006</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>2025-04-16</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Construction milestone</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Kolkata, India</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Construction commences on NPOL Acoustic Research Ship</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>GRSE begins construction of the ARS later identified as Yard 3058.</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Production start</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>Expands indigenous underwater-acoustic research infrastructure</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS_START</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R4740b1f84dc14509"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Rcf9e45927b324ae6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R3f0ef2231caa4867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="Rc015daf5d1ca4ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Rdbb4fbbdb99b438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R4aa0dc19e7ed4535"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Ra92fc581b4a44c4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R13faa0942b2549da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R2e3c8ac9e25e480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R34d6df86b3c347a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="Ra7d60b8cbf8642e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R3d5f466278be415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R47b363e394b349ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R96c6877f0402431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R26351c64fecc47fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Rda9b01b2c64249ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Raf869a8850a84ba7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R8a2020422a444931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R178cb3e3fbbe46d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R308b0362675844ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Red233728e9024be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R591db8f3ae334a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R209ad2171fd3423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R70501764c2fc4420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R8ae1a4383b33482c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R5a4f629219e04c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R019e9521a7f14bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Rb7c09ce8b9e44b3c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2386,6 +2386,325 @@
         <x:v>https://apnews.com/article/8e263817b1ad5abd49beec7a6a8f88a4</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>EXT_SEC_001</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Territorial capture / chokepoint escalation</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Maritime / Port / Trade</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Mokha / Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Houthi capture of Mokha</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>Houthis seized Mokha and advanced toward strategic Red Sea islands, increasing leverage near Bab al-Mandab.</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Port of Mokha / southern Red Sea / Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>Security exposure, routing/insurance risk and potential Saudi-linked shipping restrictions</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>https://gcaptain.com/houthis-seize-mocha-tightening-grip-on-bab-el-mandeb-and-red-sea-shipping/</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>https://splash247.com/houthis-advance-towards-bab-al-mandab-with-capture-of-mokha/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>EXT_SEC_002</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Maritime Security</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Piracy / attempted boarding</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Yemen / Gulf of Aden</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Off Balhaf / Al Mukalla approaches</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Attempted boarding of GLAMOR</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>Suspected pirates boarded GLAMOR; attackers failed to seize vessel and crew remained safe.</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>Merchant vessel / Gulf of Aden shipping</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Temporary voyage interruption; elevated piracy and security-cost exposure</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Occurred / monitoring</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>https://splash247.com/pirates-board-ship-off-yemen/</x:v>
+      </x:c>
+      <x:c r="O29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>EXT_SEC_003</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Rail infrastructure attacks</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Rail / Inland Trade</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>National rail network / locomotive depots</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Mounting attacks on Ukraine rail network</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Repeated Russian strikes target locomotives, depots and critical rail infrastructure.</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Rail freight / depots / locomotives / port hinterlands</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Freight reliability and maintenance capacity under pressure; grain/metals/containers exposed</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>Active / repeated</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>https://zalizna-rodyna.uz.gov.ua/en/memorial/volodimir-gubskiy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>EXT_SEC_004</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Navigation / Electronic Interference</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>GPS / GNSS disruption</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Maritime / Port</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Port of Klaipėda / Baltic Sea</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Klaipėda navigation resilience response</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Smart buoy and pilot fallback systems deployed in response to GPS signal disruptions.</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>Port approaches / pilotage / vessel arrivals</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Arrival planning and cargo-flow reliability exposed to persistent interference</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Active / mitigated</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>https://portofklaipeda.lt/en/naujienos/smarter-and-safer-navigation-new-buoy-begins-operating-near-the-port-of-klaipeda/</x:v>
+      </x:c>
+      <x:c r="O31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>EXT_SEC_005</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Container terminal strike</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Maritime / Port / Inland</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Terminal Cuenca del Plata / Montevideo</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Indefinite strike at Montevideo TCP</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Severe staffing restrictions reduce crane productivity and halt empty-container-yard operations.</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>Container terminal / vessel handling / yard / inland logistics</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Backlog, schedule slippage, empty-equipment constraints and customer disruption</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>https://splash247.com/indefinite-strike-hits-montevideo-container-terminal/</x:v>
+      </x:c>
+      <x:c r="O32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>EXT_SEC_006</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Critical Infrastructure Failure</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Air traffic control technical failure</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>UK airspace / major airports</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>NATS system failure</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Technical failure caused around 1,300 flight cancellations; operations restored but recovery extended into second day.</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>Air traffic control / airports / airlines / air cargo</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>Cargo capacity loss, missed connections and network backlog; not a cyberattack</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Recovery</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>https://aircargoweek.com/nats-system-failure-leaves-uk-airlines-battling-a-second-day-of-disruption/</x:v>
+      </x:c>
+      <x:c r="O33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>EXT_SEC_007</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Aviation strike</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Jomo Kenyatta International Airport / Nairobi</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Kenya aviation strike</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Strike disruption exposed concentration of East African air cargo at JKIA and limited spare recovery capacity.</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>Airport / airlines / handlers / perishables exporters</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>5,500–7,000 tonnes weekly cargo exposed; flowers and fresh produce face spoilage and missed-market risk</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>Recent / recurring</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>https://aircargoweek.com/kenya-aviation-strike-exposes-the-fragility-of-east-africas-air-cargo-gateway/</x:v>
+      </x:c>
+      <x:c r="O34"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4022,6 +4341,479 @@
       <x:c r="V26" s="14"/>
       <x:c r="W26" s="14"/>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>EXT_SEC_001</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Territorial capture / chokepoint escalation</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Port / territorial control</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Maritime / Trade</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Red Sea / Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>Mokha / Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Houthi capture of Mokha</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>Immediate / ongoing</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>Threat geometry shifts toward southern Red Sea approaches</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>Routing, insurance, Suez connectivity and Saudi-linked flows exposed</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>Houthi forces</x:v>
+      </x:c>
+      <x:c r="Q27" t="str">
+        <x:v>SRC_SEC_001</x:v>
+      </x:c>
+      <x:c r="R27" t="str">
+        <x:v>https://splash247.com/houthis-advance-towards-bab-al-mandab-with-capture-of-mokha/</x:v>
+      </x:c>
+      <x:c r="S27" t="str">
+        <x:v>https://gcaptain.com/houthis-seize-mocha-tightening-grip-on-bab-el-mandeb-and-red-sea-shipping/</x:v>
+      </x:c>
+      <x:c r="T27" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U27"/>
+      <x:c r="V27" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="W27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>EXT_SEC_002</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Maritime Security</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Piracy / attempted boarding</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Boarding</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Gulf of Aden</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>Off Balhaf / Al Mukalla</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Attempted boarding of GLAMOR</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>Occurred / monitoring</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>Crew citadel response; temporary vessel interruption</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>Piracy risk, insurance/security costs and route exposure</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>Suspected pirates</x:v>
+      </x:c>
+      <x:c r="Q28" t="str">
+        <x:v>SRC_SEC_003</x:v>
+      </x:c>
+      <x:c r="R28" t="str">
+        <x:v>https://splash247.com/pirates-board-ship-off-yemen/</x:v>
+      </x:c>
+      <x:c r="S28"/>
+      <x:c r="T28" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U28"/>
+      <x:c r="V28" t="str">
+        <x:v>Maritime Security</x:v>
+      </x:c>
+      <x:c r="W28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>EXT_SEC_003</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Rail infrastructure attacks</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Missile / strike campaign</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Rail / Inland</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Ukraine / Black Sea hinterland</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>National network</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>Mounting attacks on Ukraine rail network</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Active / repeated</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>Locomotives, depots and infrastructure damaged/targeted</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>Grain, metals, container and EU-border freight reliability threatened</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>Russian military strikes</x:v>
+      </x:c>
+      <x:c r="Q29" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="R29" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+      <x:c r="S29" t="str">
+        <x:v>https://zalizna-rodyna.uz.gov.ua/en/memorial/volodimir-gubskiy</x:v>
+      </x:c>
+      <x:c r="T29" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U29"/>
+      <x:c r="V29" t="str">
+        <x:v>Conflict / Security</x:v>
+      </x:c>
+      <x:c r="W29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>EXT_SEC_004</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Navigation / Electronic Interference</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>GPS / GNSS disruption</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Satellite-navigation interference</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Maritime / Port</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Baltic Sea</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Port of Klaipėda</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Klaipėda navigation resilience response</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Active / mitigated</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>Fallback navigation and pilotage systems required</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>Arrival planning and cargo flow may be disrupted</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>GPS interference</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>SRC_SEC_004</x:v>
+      </x:c>
+      <x:c r="R30" t="str">
+        <x:v>https://portofklaipeda.lt/en/naujienos/smarter-and-safer-navigation-new-buoy-begins-operating-near-the-port-of-klaipeda/</x:v>
+      </x:c>
+      <x:c r="S30"/>
+      <x:c r="T30" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U30"/>
+      <x:c r="V30" t="str">
+        <x:v>Electronic Interference</x:v>
+      </x:c>
+      <x:c r="W30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>EXT_SEC_005</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>Container terminal strike</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Indefinite strike</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Maritime / Port / Inland</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>South America</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Port of Montevideo / TCP</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>Indefinite strike at Montevideo TCP</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>One crane gang; empty yard unavailable</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>Container backlog, equipment imbalance and logistics delays</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>Port labour action</x:v>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:v>SRC_SEC_005</x:v>
+      </x:c>
+      <x:c r="R31" t="str">
+        <x:v>https://splash247.com/indefinite-strike-hits-montevideo-container-terminal/</x:v>
+      </x:c>
+      <x:c r="S31"/>
+      <x:c r="T31" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U31"/>
+      <x:c r="V31" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="W31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>EXT_SEC_006</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Critical Infrastructure Failure</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>Air traffic control technical failure</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>ATC system outage</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>UK airspace</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>NATS system failure</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Recovery</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>24-72h</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>Large-scale cancellations and network repositioning</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>Cargo capacity loss and missed connections</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>Technical system failure</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+      <x:c r="R32" t="str">
+        <x:v>https://aircargoweek.com/nats-system-failure-leaves-uk-airlines-battling-a-second-day-of-disruption/</x:v>
+      </x:c>
+      <x:c r="S32"/>
+      <x:c r="T32" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U32"/>
+      <x:c r="V32" t="str">
+        <x:v>Critical Infrastructure Failure</x:v>
+      </x:c>
+      <x:c r="W32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>EXT_SEC_007</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Aviation strike</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Airport / airline labour disruption</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>East Africa</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>JKIA / Nairobi</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>Kenya aviation strike</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>Recent / recurring</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>Flight cancellations and constrained recovery</x:v>
+      </x:c>
+      <x:c r="O33" t="str">
+        <x:v>Perishable exports and regional connections exposed</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
+        <x:v>Aviation labour action</x:v>
+      </x:c>
+      <x:c r="Q33" t="str">
+        <x:v>SRC_SEC_009</x:v>
+      </x:c>
+      <x:c r="R33" t="str">
+        <x:v>https://aircargoweek.com/kenya-aviation-strike-exposes-the-fragility-of-east-africas-air-cargo-gateway/</x:v>
+      </x:c>
+      <x:c r="S33"/>
+      <x:c r="T33" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="U33"/>
+      <x:c r="V33" t="str">
+        <x:v>Labour / Industrial Action</x:v>
+      </x:c>
+      <x:c r="W33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7280,6 +8072,429 @@
       </x:c>
       <x:c r="O64"/>
     </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>NEWS_SEC_001</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Houthis advance towards Bab al-Mandab with capture of Mokha</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>https://splash247.com/houthis-advance-towards-bab-al-mandab-with-capture-of-mokha/</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>Houthi seizure of Mokha brings the group closer to Bab al-Mandab and increases southern Red Sea monitoring/threat potential; Saudi-linked shipping remains specifically restricted.</x:v>
+      </x:c>
+      <x:c r="G65" t="str">
+        <x:v>Red Sea / Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="H65" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>Maritime Security / Trade</x:v>
+      </x:c>
+      <x:c r="J65" t="str">
+        <x:v>Security escalation</x:v>
+      </x:c>
+      <x:c r="K65" t="str">
+        <x:v>Territorial control / chokepoint risk</x:v>
+      </x:c>
+      <x:c r="L65" t="str">
+        <x:v>EVENT_SEC_001</x:v>
+      </x:c>
+      <x:c r="M65" t="str">
+        <x:v>Verified by multiple reporting streams</x:v>
+      </x:c>
+      <x:c r="N65" t="str">
+        <x:v>SRC_SEC_001</x:v>
+      </x:c>
+      <x:c r="O65" t="str">
+        <x:v>Trade relevance: routing, insurance, Saudi Red Sea exports, Suez connectivity and vessel arrival uncertainty.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>NEWS_SEC_002</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Pirates board ship off Yemen</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>https://splash247.com/pirates-board-ship-off-yemen/</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>Suspected pirates boarded GLAMOR off Yemen; crew sheltered in citadel, attackers failed to take control and vessel resumed voyage.</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>Gulf of Aden / Arabian Sea</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>Yemen</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>Maritime Security / Trade</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>Piracy</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>Attempted boarding</x:v>
+      </x:c>
+      <x:c r="L66" t="str">
+        <x:v>EVENT_SEC_002</x:v>
+      </x:c>
+      <x:c r="M66" t="str">
+        <x:v>Reported / UKMTO updates referenced</x:v>
+      </x:c>
+      <x:c r="N66" t="str">
+        <x:v>SRC_SEC_003</x:v>
+      </x:c>
+      <x:c r="O66" t="str">
+        <x:v>Trade relevance: Salalah–Djibouti lane, crew security, rerouting and war/piracy insurance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>NEWS_SEC_003</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Ukraine's rail network comes under mounting Russian attacks</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>International Railway Journal</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>Repeated attacks on locomotives, depots and critical rail infrastructure put Ukraine's freight network under growing pressure.</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>Europe / Black Sea hinterland</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>Rail Security / Trade</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>Infrastructure attack</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>Rail network degradation</x:v>
+      </x:c>
+      <x:c r="L67" t="str">
+        <x:v>EVENT_SEC_003</x:v>
+      </x:c>
+      <x:c r="M67" t="str">
+        <x:v>High-confidence specialist reporting</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="O67" t="str">
+        <x:v>Trade relevance: grain, metals, containers, port hinterlands and EU-border freight.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>NEWS_SEC_004</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Klaipėda deploys smart buoy to tackle GPS disruption</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>Klaipėda State Seaport Authority</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>https://portofklaipeda.lt/en/naujienos/smarter-and-safer-navigation-new-buoy-begins-operating-near-the-port-of-klaipeda/</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>New offshore buoy and pilot equipment support navigation and cargo-flow planning during GPS interference.</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>Baltic Sea</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>Lithuania</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>Port Security / Trade</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>Navigation disruption</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>GNSS interference resilience</x:v>
+      </x:c>
+      <x:c r="L68" t="str">
+        <x:v>EVENT_SEC_004</x:v>
+      </x:c>
+      <x:c r="M68" t="str">
+        <x:v>Official / primary</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>SRC_SEC_004</x:v>
+      </x:c>
+      <x:c r="O68" t="str">
+        <x:v>Trade relevance: arrival planning, pilotage reliability and container/bulk gateway continuity.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>NEWS_SEC_005</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>Indefinite strike hits Montevideo container terminal</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>Splash247</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>https://splash247.com/indefinite-strike-hits-montevideo-container-terminal/</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>TCP operates with severe labour restrictions including one crane gang and no empty-container-yard workers.</x:v>
+      </x:c>
+      <x:c r="G69" t="str">
+        <x:v>South America</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>Port Operations / Trade</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>Labour disruption</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>Container-terminal strike</x:v>
+      </x:c>
+      <x:c r="L69" t="str">
+        <x:v>EVENT_SEC_005</x:v>
+      </x:c>
+      <x:c r="M69" t="str">
+        <x:v>Reported by terminal via trade press</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>SRC_SEC_005</x:v>
+      </x:c>
+      <x:c r="O69" t="str">
+        <x:v>Trade relevance: container backlog, empty-equipment imbalance, ship productivity and inland logistics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>NEWS_SEC_006</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>NATS system failure leaves UK aviation recovering</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>Air Cargo Week</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>https://aircargoweek.com/nats-system-failure-leaves-uk-airlines-battling-a-second-day-of-disruption/</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Technical failure led to roughly 1,300 UK flight cancellations; NATS ruled out a cyberattack and network recovery continued.</x:v>
+      </x:c>
+      <x:c r="G70" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>Aviation / Trade</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>Critical infrastructure disruption</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>Air traffic control failure</x:v>
+      </x:c>
+      <x:c r="L70" t="str">
+        <x:v>EVENT_SEC_006</x:v>
+      </x:c>
+      <x:c r="M70" t="str">
+        <x:v>Reported / operator statements referenced</x:v>
+      </x:c>
+      <x:c r="N70" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+      <x:c r="O70" t="str">
+        <x:v>Trade relevance: air-cargo capacity, missed connections, crew/aircraft displacement and gateway recovery.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>NEWS_SEC_007</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Kenya aviation strike exposes East Africa air-cargo gateway</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>Air Cargo Week</x:v>
+      </x:c>
+      <x:c r="E71" t="str">
+        <x:v>https://aircargoweek.com/kenya-aviation-strike-exposes-the-fragility-of-east-africas-air-cargo-gateway/</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>JKIA disruption exposes concentrated perishables and regional air-cargo flows, with limited spare airline capacity slowing recovery.</x:v>
+      </x:c>
+      <x:c r="G71" t="str">
+        <x:v>East Africa</x:v>
+      </x:c>
+      <x:c r="H71" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>Aviation / Trade</x:v>
+      </x:c>
+      <x:c r="J71" t="str">
+        <x:v>Labour disruption</x:v>
+      </x:c>
+      <x:c r="K71" t="str">
+        <x:v>Airport / airline strike</x:v>
+      </x:c>
+      <x:c r="L71" t="str">
+        <x:v>EVENT_SEC_007</x:v>
+      </x:c>
+      <x:c r="M71" t="str">
+        <x:v>Specialist analysis</x:v>
+      </x:c>
+      <x:c r="N71" t="str">
+        <x:v>SRC_SEC_009</x:v>
+      </x:c>
+      <x:c r="O71" t="str">
+        <x:v>Trade relevance: 5,500–7,000 tonnes weekly cargo and time-sensitive flower/fresh-produce exports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>NEWS_SEC_008</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Singapore warns against false vessel identity and ownership data</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>https://shipandbunker.com/news/apac/111394-singapore-warns-port-users-against-false-vessel-identity-and-ownership-data-in-port-call-filings</x:v>
+      </x:c>
+      <x:c r="F72" t="str">
+        <x:v>MPA warns of enforcement over false vessel identity, registry, ownership, cargo and trading-history data in port-call filings.</x:v>
+      </x:c>
+      <x:c r="G72" t="str">
+        <x:v>Asia</x:v>
+      </x:c>
+      <x:c r="H72" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="I72" t="str">
+        <x:v>Maritime Compliance / Trade</x:v>
+      </x:c>
+      <x:c r="J72" t="str">
+        <x:v>Compliance enforcement</x:v>
+      </x:c>
+      <x:c r="K72" t="str">
+        <x:v>Vessel identity / port clearance</x:v>
+      </x:c>
+      <x:c r="L72" t="str">
+        <x:v>EVENT_SEC_008</x:v>
+      </x:c>
+      <x:c r="M72" t="str">
+        <x:v>Official circular confirmed</x:v>
+      </x:c>
+      <x:c r="N72" t="str">
+        <x:v>SRC_SEC_010</x:v>
+      </x:c>
+      <x:c r="O72" t="str">
+        <x:v>Trade relevance: port clearance, sanctions screening, bunkering, agency risk and potential enforcement delays.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>NEWS_SEC_009</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Bunker suppliers can no longer trust two key sanctions checks</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>Ship &amp; Bunker</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>https://shipandbunker.com/news/world/312418-feature-bunker-suppliers-can-no-longer-trust-two-key-sanctions-checks</x:v>
+      </x:c>
+      <x:c r="F73" t="str">
+        <x:v>Fraudulent registries and fabricated AIS meetings increasingly undermine vessel identity and trading-history checks used by suppliers.</x:v>
+      </x:c>
+      <x:c r="G73" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="H73" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="I73" t="str">
+        <x:v>Sanctions / Maritime Compliance</x:v>
+      </x:c>
+      <x:c r="J73" t="str">
+        <x:v>Compliance risk</x:v>
+      </x:c>
+      <x:c r="K73" t="str">
+        <x:v>False registry / AIS spoofing</x:v>
+      </x:c>
+      <x:c r="L73" t="str">
+        <x:v>EVENT_SEC_009</x:v>
+      </x:c>
+      <x:c r="M73" t="str">
+        <x:v>Industry analysis citing Windward data</x:v>
+      </x:c>
+      <x:c r="N73" t="str">
+        <x:v>SRC_SEC_011</x:v>
+      </x:c>
+      <x:c r="O73" t="str">
+        <x:v>Trade relevance: bunkering refusals, counterparty due diligence, port clearance, sanctions exposure and transaction friction.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -12444,6 +13659,294 @@
       </x:c>
       <x:c r="J39" t="str">
         <x:v>SRC_SAGAR_GRSE_ARS_START</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>EVENT_SEC_001</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Security escalation</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>PORTG0198</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Mokha / Bab al-Mandab / southern Red Sea</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Houthis seize Mokha and increase leverage near Bab al-Mandab</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Control of Mokha and reported advance toward Hanish alter the security geography around the southern Red Sea gateway.</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Higher monitoring/threat exposure for approaching shipping and Saudi-linked vessels.</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Potential insurance, routing, Suez/Red Sea transit and energy-export impacts.</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SRC_SEC_001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>EVENT_SEC_002</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Piracy / attempted boarding</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>VESSEL_GLAMOR</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>Gulf of Aden / off Yemen</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Attempted pirate boarding of GLAMOR</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Armed attackers boarded GLAMOR but failed to seize control; crew sheltered in citadel and vessel resumed voyage.</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Crew-security response and temporary voyage interruption.</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Raises piracy risk, insurance and routing concerns on Salalah–Djibouti / Gulf of Aden trade lanes.</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SRC_SEC_003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>EVENT_SEC_003</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Infrastructure attack / network degradation</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>Russian attacks intensify against Ukrainian rail network</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Repeated strikes target locomotives, depots and critical railway infrastructure.</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Reduced equipment availability, repair burden and network reliability.</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Potential effects on grain, steel, container and EU-border freight plus Black Sea port hinterlands.</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>EVENT_SEC_004</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Navigation / GNSS interference</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>PORT_KLAIPEDA</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Klaipėda, Lithuania</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Klaipėda deploys navigation fallback for GPS disruption</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Smart buoy and specialist pilot equipment provide additional reference and planning data during satellite-navigation interference.</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Improves resilience but confirms persistent GNSS interference as an operating hazard.</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Arrival planning and cargo-flow reliability remain exposed to Baltic navigation disruption.</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SRC_SEC_004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>EVENT_SEC_005</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>Labour disruption</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>TERM_TCP_MONTEVIDEO</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>Port of Montevideo, Uruguay</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>Indefinite strike constrains Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Only one crane gang available; full-container yard limited and empty-container yard unstaffed.</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Low vessel productivity, container-yard restrictions and customer disruption.</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Backlog, empty-equipment imbalance, schedule slippage and regional logistics-chain effects.</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SRC_SEC_005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>EVENT_SEC_006</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Critical infrastructure disruption</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>COMP_NATS_UK</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>NATS technical failure disrupts UK air network</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Technical failure led to around 1,300 flight cancellations; recovery continued after systems returned to normal.</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Air traffic capacity and schedules disrupted; aircraft and crews displaced.</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Air-cargo delays, missed connections and gateway backlog; incident was not assessed as cyberattack.</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>SRC_SEC_008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>EVENT_SEC_007</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>Labour disruption / air-cargo resilience</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>AIRPORT_JKIA</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Nairobi, Kenya</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Kenya aviation strike stresses East Africa cargo gateway</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Strike disruption at JKIA cascades across regional services and a highly time-sensitive export system.</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Flight cancellations and constrained recovery due limited spare capacity.</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Perishables/flower exports, worth millions over short disruption windows, face spoilage and missed-market risk.</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>SRC_SEC_009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>EVENT_SEC_008</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Compliance enforcement</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>COMP_MPA_SG</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>MPA tightens warning on false vessel and ownership data</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>Singapore warns owners/agents against false identity, registry, ownership, cargo or trading-history filings and points to sanctions and suspicious-transaction duties.</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Greater verification burden for port calls and clearance.</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Potential delays/refusals, agency liability, bunkering friction and sanctions-enforcement exposure.</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>SRC_SEC_010</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>EVENT_SEC_009</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Sanctions evasion / maritime identity risk</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>GLOBAL_MARITIME_COMPLIANCE</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>Fraudulent flags and AIS spoofing erode sanctions screening</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>Industry analysis cites 275 tankers broadcasting fraudulent registry flags in Q2 and 1.24m false ship-to-ship AIS meetings in the quarter.</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Identity and voyage-history verification becomes less reliable.</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>Higher KYC/compliance cost, bunker-supply risk, transaction friction and possible sanctions exposure.</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>SRC_SEC_011</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -57857,6 +59360,294 @@
         <x:v>SRC132_003</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>IMPACT_SEC_001</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>EVENT_SEC_001</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Maritime / Trade</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>Chokepoint security escalation</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Bab al-Mandab / Red Sea</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Active / developing</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Immediate / ongoing</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Threat geometry shifts closer to shipping approaches</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>Insurance/routing pressure; Saudi-linked cargo and Red Sea/Suez flows exposed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>IMPACT_SEC_002</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>EVENT_SEC_002</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Maritime</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Piracy / boarding</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Gulf of Aden</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Occurred / monitoring</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Citadel response; temporary voyage disruption</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Potential rerouting, security costs and insurance increases</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>IMPACT_SEC_003</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>EVENT_SEC_003</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Rail / Trade</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>Infrastructure degradation</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Ukraine national rail network</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Active / repeated</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>Locomotive/depot availability and maintenance capacity under pressure</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>Grain/metals/container corridors and port hinterlands face reliability/capacity risk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>IMPACT_SEC_004</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>EVENT_SEC_004</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Maritime / Port</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>GNSS interference</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Port of Klaipėda / Baltic</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Persistent / mitigated</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Pilotage and arrival planning require fallback systems</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>Gateway flow planning and schedule reliability exposed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>IMPACT_SEC_005</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>EVENT_SEC_005</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Maritime / Port / Inland</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>Labour stoppage</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Port of Montevideo / TCP</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>One crane gang; empty yard unavailable</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>Container backlog, equipment imbalance and customer delays</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>IMPACT_SEC_006</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>EVENT_SEC_006</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>ATC technical failure</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>Recovery</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>24-72h</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Flight cancellations and network repositioning</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>Cargo capacity loss, missed connections and backlog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>IMPACT_SEC_007</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>EVENT_SEC_007</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Aviation / Air Cargo</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Labour stoppage</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>JKIA / East Africa</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>Recent / recurring</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Flight disruption and constrained recovery</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>Perishables and regional exports face spoilage and market-access risk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>IMPACT_SEC_008</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>EVENT_SEC_008</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Maritime / Compliance</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Port-clearance enforcement</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>Singapore</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>Active policy</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Moderate</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>More stringent identity/ownership/document checks</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Clearance delays, sanctions screening and bunkering counterparty risk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>IMPACT_SEC_009</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>EVENT_SEC_009</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Maritime / Compliance</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Identity and AIS integrity failure</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Global tanker / bunker market</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Active trend</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Ongoing</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Vessel identity and voyage-history checks less reliable</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>Higher KYC cost, supply refusals and sanctions exposure</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/09_intelligence.xlsx
+++ b/data/09_intelligence.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R26351c64fecc47fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="Rda9b01b2c64249ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="Raf869a8850a84ba7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R8a2020422a444931"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="R178cb3e3fbbe46d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="R308b0362675844ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="Red233728e9024be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R591db8f3ae334a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R209ad2171fd3423a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R70501764c2fc4420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="R8ae1a4383b33482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R5a4f629219e04c15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="R019e9521a7f14bce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="Rb7c09ce8b9e44b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rbc16417472024227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Registry" sheetId="2" r:id="R1a73d169223448b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Entity Links" sheetId="3" r:id="R61d51a7598a54eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Events" sheetId="4" r:id="R1e501b681b954caa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Observations" sheetId="5" r:id="Ra99f3c1fde434fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Entity Links" sheetId="6" r:id="Rc1e6a729b78547b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Impacts" sheetId="7" r:id="R88c3e242e3454373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Taxonomy" sheetId="8" r:id="R1b1fdd4a62e046bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Ingestion Map" sheetId="9" r:id="R220ca8bee49f48d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring" sheetId="10" r:id="R38743ad5aea6433d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Event Links" sheetId="11" r:id="Rb7db1ac7f6304ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disruption Watch" sheetId="12" r:id="R0e5d13a5b9014c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Disruptions" sheetId="13" r:id="Rd52e0775eeb74eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weather Labour Events" sheetId="14" r:id="R3514755280da4fcf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58251,6 +58251,36 @@
       </x:c>
       <x:c r="J60"/>
     </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>ELINK_SEC_PORT_001</x:v>
+      </x:c>
+      <x:c r="B61"/>
+      <x:c r="C61" t="str">
+        <x:v>EVENT_SEC_005</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>PORTG0206</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>Port</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>AFFECTED_PARENT_PORT</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>Terminal TERM_TCP_MONTEVIDEO child-of-port relationship</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>security_trade_backfill</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>Allows Port of Montevideo detail page to surface TCP strike.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
